--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\CSHYEON\Data\git\game\c++\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89B854A4-393A-485D-87A8-E80EB7D2F7EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76693FC3-4059-4271-98AA-CDE47E16E6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="670">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1980,16 +1980,10 @@
     <t>INPUT</t>
   </si>
   <si>
-    <t>UNKNOWN1</t>
-  </si>
-  <si>
     <t>NORMAL</t>
   </si>
   <si>
     <t>TARGET</t>
-  </si>
-  <si>
-    <t>UNKNOWN2</t>
   </si>
   <si>
     <t>UNKNOWN3</t>
@@ -2482,7 +2476,7 @@
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>4</v>
@@ -2545,7 +2539,7 @@
         <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>41</v>
@@ -2596,7 +2590,7 @@
         <v>49</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>50</v>
@@ -2610,7 +2604,7 @@
         <v>18</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>51</v>
@@ -2627,7 +2621,7 @@
         <v>53</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>54</v>
@@ -2644,7 +2638,7 @@
         <v>55</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>56</v>
@@ -2729,7 +2723,7 @@
         <v>66</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>67</v>
@@ -2806,7 +2800,7 @@
         <v>76</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>77</v>
@@ -2823,7 +2817,7 @@
         <v>78</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>79</v>
@@ -2840,7 +2834,7 @@
         <v>81</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>82</v>
@@ -2857,7 +2851,7 @@
         <v>84</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>85</v>
@@ -2874,7 +2868,7 @@
         <v>86</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>87</v>
@@ -2891,7 +2885,7 @@
         <v>88</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>89</v>
@@ -2908,7 +2902,7 @@
         <v>90</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>91</v>
@@ -2925,7 +2919,7 @@
         <v>93</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>94</v>
@@ -2942,7 +2936,7 @@
         <v>96</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>97</v>
@@ -2959,7 +2953,7 @@
         <v>99</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>100</v>
@@ -2976,7 +2970,7 @@
         <v>101</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>102</v>
@@ -2990,7 +2984,7 @@
         <v>103</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>104</v>
@@ -3004,7 +2998,7 @@
         <v>105</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>106</v>
@@ -3018,7 +3012,7 @@
         <v>108</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>109</v>
@@ -3032,7 +3026,7 @@
         <v>111</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>112</v>
@@ -3046,7 +3040,7 @@
         <v>114</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>115</v>
@@ -3060,7 +3054,7 @@
         <v>116</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>117</v>
@@ -3074,7 +3068,7 @@
         <v>118</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>119</v>
@@ -3088,7 +3082,7 @@
         <v>120</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>121</v>
@@ -3102,7 +3096,7 @@
         <v>123</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>124</v>
@@ -3116,7 +3110,7 @@
         <v>125</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>126</v>
@@ -3133,7 +3127,7 @@
         <v>128</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>129</v>
@@ -3167,7 +3161,7 @@
         <v>135</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>136</v>
@@ -3204,7 +3198,7 @@
         <v>141</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>142</v>
@@ -3261,7 +3255,7 @@
         <v>150</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>151</v>
@@ -3275,7 +3269,7 @@
         <v>153</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>154</v>
@@ -3292,7 +3286,7 @@
         <v>156</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>157</v>
@@ -3309,7 +3303,7 @@
         <v>159</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>160</v>
@@ -3326,7 +3320,7 @@
         <v>162</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>163</v>
@@ -3343,7 +3337,7 @@
         <v>165</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>166</v>
@@ -3360,7 +3354,7 @@
         <v>168</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>169</v>
@@ -3377,7 +3371,7 @@
         <v>171</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>172</v>
@@ -3391,7 +3385,7 @@
         <v>174</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>175</v>
@@ -3405,7 +3399,7 @@
         <v>177</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>178</v>
@@ -3419,7 +3413,7 @@
         <v>180</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>181</v>
@@ -3433,7 +3427,7 @@
         <v>183</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>184</v>
@@ -3447,7 +3441,7 @@
         <v>186</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>187</v>
@@ -3461,7 +3455,7 @@
         <v>189</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>190</v>
@@ -3475,7 +3469,7 @@
         <v>192</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>193</v>
@@ -3489,7 +3483,7 @@
         <v>195</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>196</v>
@@ -3503,7 +3497,7 @@
         <v>198</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>199</v>
@@ -3523,7 +3517,7 @@
         <v>201</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>202</v>
@@ -3540,7 +3534,7 @@
         <v>204</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>205</v>
@@ -3554,7 +3548,7 @@
         <v>207</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>208</v>
@@ -3568,7 +3562,7 @@
         <v>210</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>211</v>
@@ -3588,7 +3582,7 @@
         <v>213</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>214</v>
@@ -3605,7 +3599,7 @@
         <v>216</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>217</v>
@@ -3622,7 +3616,7 @@
         <v>219</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>220</v>
@@ -3639,7 +3633,7 @@
         <v>222</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>223</v>
@@ -3656,7 +3650,7 @@
         <v>225</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>226</v>
@@ -3673,7 +3667,7 @@
         <v>228</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>229</v>
@@ -3690,7 +3684,7 @@
         <v>231</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>232</v>
@@ -3707,7 +3701,7 @@
         <v>234</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>235</v>
@@ -3724,7 +3718,7 @@
         <v>237</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>238</v>
@@ -3741,7 +3735,7 @@
         <v>240</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>241</v>
@@ -3758,7 +3752,7 @@
         <v>243</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>244</v>
@@ -3775,7 +3769,7 @@
         <v>246</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>247</v>
@@ -3792,7 +3786,7 @@
         <v>249</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>250</v>
@@ -3809,7 +3803,7 @@
         <v>252</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>253</v>
@@ -3826,7 +3820,7 @@
         <v>255</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>256</v>
@@ -3843,7 +3837,7 @@
         <v>258</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>259</v>
@@ -3860,7 +3854,7 @@
         <v>261</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>262</v>
@@ -3877,7 +3871,7 @@
         <v>264</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>265</v>
@@ -3894,7 +3888,7 @@
         <v>267</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>268</v>
@@ -3911,7 +3905,7 @@
         <v>270</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>271</v>
@@ -3928,7 +3922,7 @@
         <v>273</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>274</v>
@@ -3942,7 +3936,7 @@
         <v>276</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>277</v>
@@ -3956,7 +3950,7 @@
         <v>279</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>280</v>
@@ -3970,7 +3964,7 @@
         <v>282</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>283</v>
@@ -3984,7 +3978,7 @@
         <v>285</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>286</v>
@@ -3998,7 +3992,7 @@
         <v>288</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>289</v>
@@ -4012,7 +4006,7 @@
         <v>291</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>292</v>
@@ -4026,7 +4020,7 @@
         <v>294</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>295</v>
@@ -4040,7 +4034,7 @@
         <v>297</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>298</v>
@@ -4054,7 +4048,7 @@
         <v>300</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D98" s="1" t="s">
         <v>301</v>
@@ -4068,7 +4062,7 @@
         <v>303</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>304</v>
@@ -4082,7 +4076,7 @@
         <v>306</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>307</v>
@@ -4096,7 +4090,7 @@
         <v>309</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>310</v>
@@ -4110,7 +4104,7 @@
         <v>312</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>313</v>
@@ -4124,7 +4118,7 @@
         <v>315</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>316</v>
@@ -4138,7 +4132,7 @@
         <v>318</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D104" s="1" t="s">
         <v>319</v>
@@ -4152,7 +4146,7 @@
         <v>321</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>322</v>
@@ -4166,7 +4160,7 @@
         <v>324</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>325</v>
@@ -4180,7 +4174,7 @@
         <v>327</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>328</v>
@@ -4194,7 +4188,7 @@
         <v>330</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>331</v>
@@ -4208,7 +4202,7 @@
         <v>333</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D109" s="1" t="s">
         <v>334</v>
@@ -4225,7 +4219,7 @@
         <v>336</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D110" s="1" t="s">
         <v>337</v>
@@ -4242,7 +4236,7 @@
         <v>339</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D111" s="1" t="s">
         <v>340</v>
@@ -4259,7 +4253,7 @@
         <v>342</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>343</v>
@@ -4273,7 +4267,7 @@
         <v>345</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D113" s="1" t="s">
         <v>346</v>
@@ -4287,7 +4281,7 @@
         <v>348</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D114" s="1" t="s">
         <v>349</v>
@@ -4304,7 +4298,7 @@
         <v>351</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D115" s="1" t="s">
         <v>352</v>
@@ -4324,7 +4318,7 @@
         <v>354</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D116" s="1" t="s">
         <v>355</v>
@@ -4344,7 +4338,7 @@
         <v>357</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>629</v>
@@ -4358,7 +4352,7 @@
         <v>359</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D118" s="1" t="s">
         <v>360</v>
@@ -4378,7 +4372,7 @@
         <v>362</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D119" s="1" t="s">
         <v>363</v>
@@ -4398,7 +4392,7 @@
         <v>365</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D120" s="1" t="s">
         <v>366</v>
@@ -4421,7 +4415,7 @@
         <v>368</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>369</v>
@@ -4438,7 +4432,7 @@
         <v>371</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D122" s="1" t="s">
         <v>372</v>
@@ -4455,7 +4449,7 @@
         <v>374</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>375</v>
@@ -4475,7 +4469,7 @@
         <v>377</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>378</v>
@@ -4489,7 +4483,7 @@
         <v>380</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>381</v>
@@ -4506,7 +4500,7 @@
         <v>383</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>384</v>
@@ -4529,7 +4523,7 @@
         <v>386</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>630</v>
@@ -4560,7 +4554,7 @@
         <v>391</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>392</v>
@@ -4574,7 +4568,7 @@
         <v>394</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>395</v>
@@ -4594,7 +4588,7 @@
         <v>397</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>398</v>
@@ -4614,7 +4608,7 @@
         <v>400</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>401</v>
@@ -4631,7 +4625,7 @@
         <v>403</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>404</v>
@@ -4648,7 +4642,7 @@
         <v>406</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>407</v>
@@ -4665,7 +4659,7 @@
         <v>409</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>410</v>
@@ -4682,7 +4676,7 @@
         <v>412</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>413</v>
@@ -4702,7 +4696,7 @@
         <v>415</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>416</v>
@@ -4719,7 +4713,7 @@
         <v>418</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>419</v>
@@ -4736,7 +4730,7 @@
         <v>421</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>422</v>
@@ -4753,7 +4747,7 @@
         <v>424</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>425</v>
@@ -4770,7 +4764,7 @@
         <v>427</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>428</v>
@@ -4787,7 +4781,7 @@
         <v>430</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>431</v>
@@ -4804,7 +4798,7 @@
         <v>433</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>434</v>
@@ -4824,7 +4818,7 @@
         <v>436</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>437</v>
@@ -4841,7 +4835,7 @@
         <v>439</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>440</v>
@@ -4861,7 +4855,7 @@
         <v>442</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>443</v>
@@ -4878,7 +4872,7 @@
         <v>445</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>446</v>
@@ -4895,7 +4889,7 @@
         <v>448</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>449</v>
@@ -4912,7 +4906,7 @@
         <v>451</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>452</v>
@@ -4929,7 +4923,7 @@
         <v>454</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D150" s="1" t="s">
         <v>455</v>
@@ -4946,7 +4940,7 @@
         <v>457</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>458</v>
@@ -4963,7 +4957,7 @@
         <v>460</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>461</v>
@@ -4977,7 +4971,7 @@
         <v>125</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>126</v>
@@ -4991,7 +4985,7 @@
         <v>464</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>465</v>
@@ -5008,7 +5002,7 @@
         <v>467</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>468</v>
@@ -5025,7 +5019,7 @@
         <v>470</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>471</v>
@@ -5039,7 +5033,7 @@
         <v>473</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>474</v>
@@ -5056,7 +5050,7 @@
         <v>476</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>477</v>
@@ -5070,7 +5064,7 @@
         <v>479</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>480</v>
@@ -5087,7 +5081,7 @@
         <v>482</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>483</v>
@@ -5101,7 +5095,7 @@
         <v>485</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>486</v>
@@ -5118,7 +5112,7 @@
         <v>488</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>489</v>
@@ -5132,7 +5126,7 @@
         <v>491</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>492</v>
@@ -5149,7 +5143,7 @@
         <v>494</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>495</v>
@@ -5166,7 +5160,7 @@
         <v>497</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>498</v>
@@ -5183,7 +5177,7 @@
         <v>500</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>501</v>
@@ -5197,7 +5191,7 @@
         <v>503</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>504</v>
@@ -5211,7 +5205,7 @@
         <v>506</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>507</v>
@@ -5228,7 +5222,7 @@
         <v>509</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>510</v>
@@ -5279,7 +5273,7 @@
         <v>518</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>519</v>
@@ -5344,7 +5338,7 @@
         <v>532</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>533</v>
@@ -5361,7 +5355,7 @@
         <v>535</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>536</v>
@@ -5375,7 +5369,7 @@
         <v>538</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>539</v>
@@ -5389,7 +5383,7 @@
         <v>541</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>542</v>
@@ -5403,7 +5397,7 @@
         <v>544</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>545</v>
@@ -5417,7 +5411,7 @@
         <v>547</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>548</v>
@@ -5434,7 +5428,7 @@
         <v>550</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>551</v>
@@ -5451,7 +5445,7 @@
         <v>553</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>554</v>
@@ -5468,7 +5462,7 @@
         <v>556</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>557</v>
@@ -5485,7 +5479,7 @@
         <v>559</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>560</v>
@@ -5502,7 +5496,7 @@
         <v>562</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>563</v>
@@ -5519,7 +5513,7 @@
         <v>565</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>566</v>
@@ -5536,7 +5530,7 @@
         <v>568</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D188" s="1" t="s">
         <v>569</v>
@@ -5553,7 +5547,7 @@
         <v>571</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>572</v>
@@ -5567,7 +5561,7 @@
         <v>574</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>575</v>
@@ -5581,7 +5575,7 @@
         <v>577</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>631</v>
@@ -5595,7 +5589,7 @@
         <v>579</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>632</v>
@@ -5609,7 +5603,7 @@
         <v>581</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>633</v>
@@ -5623,7 +5617,7 @@
         <v>583</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>584</v>
@@ -5640,7 +5634,7 @@
         <v>586</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>634</v>
@@ -5654,7 +5648,7 @@
         <v>588</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F196" s="1" t="s">
         <v>635</v>
@@ -5668,7 +5662,7 @@
         <v>590</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>636</v>
@@ -5682,7 +5676,7 @@
         <v>592</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>637</v>
@@ -5696,7 +5690,7 @@
         <v>594</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E199" s="1" t="s">
         <v>595</v>
@@ -5713,7 +5707,7 @@
         <v>597</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E200" s="1" t="s">
         <v>598</v>
@@ -5730,7 +5724,7 @@
         <v>600</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="E201" s="1" t="s">
         <v>601</v>
@@ -5747,7 +5741,7 @@
         <v>603</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F202" s="1" t="s">
         <v>638</v>
@@ -5761,7 +5755,7 @@
         <v>605</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>606</v>
@@ -5775,7 +5769,7 @@
         <v>608</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F204" s="1" t="s">
         <v>639</v>
@@ -5789,7 +5783,7 @@
         <v>610</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>640</v>
@@ -5803,7 +5797,7 @@
         <v>612</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>613</v>
@@ -5817,7 +5811,7 @@
         <v>615</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>616</v>
@@ -5831,7 +5825,7 @@
         <v>618</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F208" s="1" t="s">
         <v>641</v>
@@ -5845,7 +5839,7 @@
         <v>620</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>642</v>
@@ -5859,7 +5853,7 @@
         <v>622</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F210" s="1" t="s">
         <v>643</v>
@@ -5873,7 +5867,7 @@
         <v>624</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>625</v>
@@ -5887,7 +5881,7 @@
         <v>627</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="F212" s="1" t="s">
         <v>644</v>
@@ -5895,86 +5889,86 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="B213" s="1" t="s">
         <v>666</v>
       </c>
-      <c r="B213" s="1" t="s">
+      <c r="C213" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="F213" s="1" t="s">
         <v>668</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>649</v>
-      </c>
-      <c r="F213" s="1" t="s">
-        <v>670</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="B214" s="1" t="s">
         <v>667</v>
       </c>
-      <c r="B214" s="1" t="s">
+      <c r="C214" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="D214" s="1" t="s">
         <v>669</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>650</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>671</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B215" s="1" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B216" s="1" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B217" s="1" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76693FC3-4059-4271-98AA-CDE47E16E6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA68C5B-9211-4045-BB52-EE6966564211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2047,6 +2047,14 @@
   </si>
   <si>
     <t>scripts/spell/청룡마령참.lua</t>
+  </si>
+  <si>
+    <t>// 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2421,7 +2429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7A1E07-EEF2-4E86-80A0-A85D709C37E7}">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:H218"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -2445,7 +2453,7 @@
     <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2467,8 +2475,11 @@
       <c r="G1" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2491,7 +2502,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -2513,8 +2524,11 @@
       <c r="G3" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H3" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2530,8 +2544,11 @@
       <c r="G4" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H4" s="1" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -2548,7 +2565,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -2565,7 +2582,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -2582,7 +2599,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
@@ -2596,7 +2613,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -2613,7 +2630,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -2630,7 +2647,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>15</v>
       </c>
@@ -2647,7 +2664,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>11</v>
       </c>
@@ -2664,7 +2681,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>9</v>
       </c>
@@ -2681,7 +2698,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
@@ -2698,7 +2715,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -2715,7 +2732,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA68C5B-9211-4045-BB52-EE6966564211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F050AAD8-5824-49DA-848F-074E9607E9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2049,11 +2049,11 @@
     <t>scripts/spell/청룡마령참.lua</t>
   </si>
   <si>
-    <t>// 구현</t>
+    <t>O</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>O</t>
+    <t># 구현</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2476,7 +2476,7 @@
         <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2501,6 +2501,9 @@
       <c r="G2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>671</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -2545,7 +2548,7 @@
         <v>39</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2564,6 +2567,9 @@
       <c r="G5" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
@@ -2580,6 +2586,9 @@
       </c>
       <c r="G6" s="1" t="s">
         <v>45</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F050AAD8-5824-49DA-848F-074E9607E9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8FD961-60EE-4A7E-898C-1846F7F9BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2607,6 +2607,9 @@
       <c r="G7" s="1" t="s">
         <v>48</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B8FD961-60EE-4A7E-898C-1846F7F9BA5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E8B246-794B-46D2-8B30-985CFB4B4637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2692,6 +2692,9 @@
       <c r="G12" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="H12" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
@@ -2709,6 +2712,9 @@
       <c r="G13" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="H13" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
@@ -2726,6 +2732,9 @@
       <c r="G14" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="H14" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
@@ -2743,6 +2752,9 @@
       <c r="G15" s="1" t="s">
         <v>59</v>
       </c>
+      <c r="H15" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
@@ -5116,7 +5128,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
         <v>484</v>
       </c>
@@ -5133,7 +5145,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
         <v>487</v>
       </c>
@@ -5147,7 +5159,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
         <v>490</v>
       </c>
@@ -5164,7 +5176,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
         <v>493</v>
       </c>
@@ -5181,7 +5193,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
         <v>496</v>
       </c>
@@ -5198,7 +5210,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
         <v>499</v>
       </c>
@@ -5212,7 +5224,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
         <v>502</v>
       </c>
@@ -5226,7 +5238,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
         <v>505</v>
       </c>
@@ -5243,7 +5255,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
         <v>508</v>
       </c>
@@ -5260,7 +5272,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
         <v>511</v>
       </c>
@@ -5277,7 +5289,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
         <v>514</v>
       </c>
@@ -5294,7 +5306,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
         <v>517</v>
       </c>
@@ -5308,7 +5320,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
         <v>520</v>
       </c>
@@ -5325,7 +5337,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
         <v>524</v>
       </c>
@@ -5342,7 +5354,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
         <v>528</v>
       </c>
@@ -5358,8 +5370,11 @@
       <c r="G175" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H175" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
         <v>531</v>
       </c>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E8B246-794B-46D2-8B30-985CFB4B4637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852D5451-E43C-40AB-9303-3B0EC614CE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3045,7 +3045,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>107</v>
       </c>
@@ -3059,7 +3059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>110</v>
       </c>
@@ -3073,7 +3073,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>113</v>
       </c>
@@ -3087,7 +3087,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>29</v>
       </c>
@@ -3101,7 +3101,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>30</v>
       </c>
@@ -3115,7 +3115,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>31</v>
       </c>
@@ -3129,7 +3129,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>122</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>32</v>
       </c>
@@ -3159,8 +3159,11 @@
       <c r="G40" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H40" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>127</v>
       </c>
@@ -3174,7 +3177,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>130</v>
       </c>
@@ -3194,7 +3197,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>134</v>
       </c>
@@ -3211,7 +3214,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>137</v>
       </c>
@@ -3231,7 +3234,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>140</v>
       </c>
@@ -3248,7 +3251,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>143</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>146</v>
       </c>
@@ -3288,7 +3291,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>149</v>
       </c>
@@ -4868,7 +4871,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
         <v>438</v>
       </c>
@@ -4888,7 +4891,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
         <v>441</v>
       </c>
@@ -4905,7 +4908,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
         <v>444</v>
       </c>
@@ -4922,7 +4925,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
         <v>447</v>
       </c>
@@ -4939,7 +4942,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
         <v>450</v>
       </c>
@@ -4956,7 +4959,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
         <v>453</v>
       </c>
@@ -4973,7 +4976,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
         <v>456</v>
       </c>
@@ -4990,7 +4993,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
         <v>459</v>
       </c>
@@ -5003,8 +5006,11 @@
       <c r="D152" s="1" t="s">
         <v>461</v>
       </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H152" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="1" t="s">
         <v>462</v>
       </c>
@@ -5017,8 +5023,11 @@
       <c r="D153" s="1" t="s">
         <v>126</v>
       </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H153" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
         <v>463</v>
       </c>
@@ -5034,8 +5043,11 @@
       <c r="G154" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H154" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
         <v>466</v>
       </c>
@@ -5051,8 +5063,11 @@
       <c r="G155" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H155" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
         <v>469</v>
       </c>
@@ -5065,8 +5080,11 @@
       <c r="D156" s="1" t="s">
         <v>471</v>
       </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H156" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
         <v>472</v>
       </c>
@@ -5082,8 +5100,11 @@
       <c r="G157" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H157" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
         <v>475</v>
       </c>
@@ -5091,13 +5112,16 @@
         <v>476</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>477</v>
       </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G158" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
         <v>478</v>
       </c>
@@ -5113,8 +5137,11 @@
       <c r="G159" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H159" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
         <v>481</v>
       </c>
@@ -5122,10 +5149,13 @@
         <v>482</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>483</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
@@ -5144,6 +5174,9 @@
       <c r="G161" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H161" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
@@ -5153,10 +5186,13 @@
         <v>488</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>489</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
@@ -5175,6 +5211,9 @@
       <c r="G163" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H163" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
@@ -5209,6 +5248,9 @@
       <c r="G165" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H165" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
@@ -5253,6 +5295,9 @@
       </c>
       <c r="G168" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852D5451-E43C-40AB-9303-3B0EC614CE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB6001A-4701-493B-9EE5-C0C0DA29E292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3553,7 +3553,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>200</v>
       </c>
@@ -3570,7 +3570,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>203</v>
       </c>
@@ -3584,7 +3584,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>206</v>
       </c>
@@ -3598,7 +3598,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>209</v>
       </c>
@@ -3617,8 +3617,11 @@
       <c r="G68" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H68" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>212</v>
       </c>
@@ -3634,8 +3637,11 @@
       <c r="G69" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H69" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>215</v>
       </c>
@@ -3651,8 +3657,11 @@
       <c r="G70" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H70" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>218</v>
       </c>
@@ -3668,8 +3677,11 @@
       <c r="G71" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H71" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>221</v>
       </c>
@@ -3685,8 +3697,11 @@
       <c r="G72" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H72" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>224</v>
       </c>
@@ -3702,8 +3717,11 @@
       <c r="G73" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H73" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>227</v>
       </c>
@@ -3719,8 +3737,11 @@
       <c r="G74" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H74" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>230</v>
       </c>
@@ -3736,8 +3757,11 @@
       <c r="G75" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H75" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>233</v>
       </c>
@@ -3753,8 +3777,11 @@
       <c r="G76" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H76" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>236</v>
       </c>
@@ -3770,8 +3797,11 @@
       <c r="G77" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H77" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>239</v>
       </c>
@@ -3787,8 +3817,11 @@
       <c r="G78" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H78" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>242</v>
       </c>
@@ -3804,8 +3837,11 @@
       <c r="G79" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H79" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>245</v>
       </c>
@@ -3821,8 +3857,11 @@
       <c r="G80" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H80" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>248</v>
       </c>
@@ -3838,8 +3877,11 @@
       <c r="G81" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H81" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>251</v>
       </c>
@@ -3855,8 +3897,11 @@
       <c r="G82" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H82" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>254</v>
       </c>
@@ -3872,8 +3917,11 @@
       <c r="G83" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H83" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>257</v>
       </c>
@@ -3889,8 +3937,11 @@
       <c r="G84" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H84" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>260</v>
       </c>
@@ -3906,8 +3957,11 @@
       <c r="G85" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H85" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>263</v>
       </c>
@@ -3923,8 +3977,11 @@
       <c r="G86" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H86" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>266</v>
       </c>
@@ -3940,8 +3997,11 @@
       <c r="G87" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H87" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>269</v>
       </c>
@@ -3957,8 +4017,11 @@
       <c r="G88" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H88" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>272</v>
       </c>
@@ -3972,7 +4035,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>275</v>
       </c>
@@ -3986,7 +4049,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>278</v>
       </c>
@@ -4000,7 +4063,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>281</v>
       </c>
@@ -4014,7 +4077,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>284</v>
       </c>
@@ -4028,7 +4091,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>287</v>
       </c>
@@ -4042,7 +4105,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>290</v>
       </c>
@@ -4056,7 +4119,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>293</v>
       </c>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FB6001A-4701-493B-9EE5-C0C0DA29E292}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DBB1E-B91E-4165-801C-9787F2063A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-180" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -4034,6 +4034,9 @@
       <c r="D89" s="1" t="s">
         <v>274</v>
       </c>
+      <c r="H89" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
@@ -4048,6 +4051,9 @@
       <c r="D90" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="H90" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
@@ -4062,6 +4068,9 @@
       <c r="D91" s="1" t="s">
         <v>280</v>
       </c>
+      <c r="H91" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
@@ -4076,6 +4085,9 @@
       <c r="D92" s="1" t="s">
         <v>283</v>
       </c>
+      <c r="H92" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
@@ -4090,6 +4102,9 @@
       <c r="D93" s="1" t="s">
         <v>286</v>
       </c>
+      <c r="H93" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
@@ -4104,6 +4119,9 @@
       <c r="D94" s="1" t="s">
         <v>289</v>
       </c>
+      <c r="H94" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
@@ -4118,6 +4136,9 @@
       <c r="D95" s="1" t="s">
         <v>292</v>
       </c>
+      <c r="H95" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
@@ -4132,8 +4153,11 @@
       <c r="D96" s="1" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H96" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>296</v>
       </c>
@@ -4146,8 +4170,11 @@
       <c r="D97" s="1" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H97" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>299</v>
       </c>
@@ -4160,8 +4187,11 @@
       <c r="D98" s="1" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H98" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>302</v>
       </c>
@@ -4174,8 +4204,11 @@
       <c r="D99" s="1" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H99" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>305</v>
       </c>
@@ -4188,8 +4221,11 @@
       <c r="D100" s="1" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H100" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>308</v>
       </c>
@@ -4202,8 +4238,11 @@
       <c r="D101" s="1" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H101" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>311</v>
       </c>
@@ -4216,8 +4255,11 @@
       <c r="D102" s="1" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H102" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>314</v>
       </c>
@@ -4230,8 +4272,11 @@
       <c r="D103" s="1" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H103" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>317</v>
       </c>
@@ -4244,8 +4289,11 @@
       <c r="D104" s="1" t="s">
         <v>319</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H104" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>320</v>
       </c>
@@ -4258,8 +4306,11 @@
       <c r="D105" s="1" t="s">
         <v>322</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H105" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>323</v>
       </c>
@@ -4272,8 +4323,11 @@
       <c r="D106" s="1" t="s">
         <v>325</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H106" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>326</v>
       </c>
@@ -4286,8 +4340,11 @@
       <c r="D107" s="1" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H107" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>329</v>
       </c>
@@ -4300,8 +4357,11 @@
       <c r="D108" s="1" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H108" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>332</v>
       </c>
@@ -4318,7 +4378,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>335</v>
       </c>
@@ -4335,7 +4395,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>338</v>
       </c>
@@ -4352,7 +4412,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>341</v>
       </c>
@@ -4653,7 +4713,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>390</v>
       </c>
@@ -4666,8 +4726,11 @@
       <c r="D129" s="1" t="s">
         <v>392</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H129" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>393</v>
       </c>
@@ -4687,7 +4750,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>396</v>
       </c>
@@ -4707,7 +4770,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>399</v>
       </c>
@@ -4724,7 +4787,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>402</v>
       </c>
@@ -4741,7 +4804,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>405</v>
       </c>
@@ -4758,7 +4821,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>408</v>
       </c>
@@ -4775,7 +4838,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>411</v>
       </c>
@@ -4795,7 +4858,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
         <v>414</v>
       </c>
@@ -4812,7 +4875,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
         <v>417</v>
       </c>
@@ -4829,7 +4892,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
         <v>420</v>
       </c>
@@ -4846,7 +4909,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
         <v>423</v>
       </c>
@@ -4863,7 +4926,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
         <v>426</v>
       </c>
@@ -4879,8 +4942,11 @@
       <c r="G141" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H141" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
         <v>429</v>
       </c>
@@ -4897,7 +4963,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
         <v>432</v>
       </c>
@@ -4917,7 +4983,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
         <v>435</v>
       </c>
@@ -5183,6 +5249,9 @@
       <c r="G158" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H158" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
@@ -5220,6 +5289,9 @@
       <c r="G160" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H160" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
@@ -5257,6 +5329,9 @@
       <c r="G162" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H162" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
@@ -5293,6 +5368,9 @@
       </c>
       <c r="G164" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\cshyeon\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641DBB1E-B91E-4165-801C-9787F2063A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56708731-47D0-4C38-B411-A7D48DF2E9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2773,7 +2773,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>68</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>80</v>
       </c>
@@ -2884,7 +2884,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>83</v>
       </c>
@@ -2901,7 +2901,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2934,8 +2934,11 @@
       <c r="E25" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H25" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>25</v>
       </c>
@@ -2951,8 +2954,11 @@
       <c r="E26" s="1" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>92</v>
       </c>
@@ -2968,8 +2974,11 @@
       <c r="E27" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H27" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>95</v>
       </c>
@@ -2985,8 +2994,11 @@
       <c r="E28" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H28" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>98</v>
       </c>
@@ -3002,8 +3014,11 @@
       <c r="E29" s="1" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H29" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>26</v>
       </c>
@@ -3016,8 +3031,11 @@
       <c r="D30" s="1" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H30" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>27</v>
       </c>
@@ -3030,8 +3048,11 @@
       <c r="D31" s="1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H31" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>28</v>
       </c>
@@ -3043,6 +3064,9 @@
       </c>
       <c r="D32" s="1" t="s">
         <v>106</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
@@ -3058,6 +3082,9 @@
       <c r="D33" s="1" t="s">
         <v>109</v>
       </c>
+      <c r="H33" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
@@ -3072,6 +3099,9 @@
       <c r="D34" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="H34" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
@@ -3086,6 +3116,9 @@
       <c r="D35" s="1" t="s">
         <v>115</v>
       </c>
+      <c r="H35" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
@@ -3196,6 +3229,9 @@
       <c r="G42" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="H42" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
@@ -3233,6 +3269,9 @@
       <c r="G44" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="H44" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
@@ -3270,6 +3309,9 @@
       <c r="G46" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="H46" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
@@ -3290,6 +3332,9 @@
       <c r="G47" s="1" t="s">
         <v>133</v>
       </c>
+      <c r="H47" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
@@ -3305,7 +3350,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>152</v>
       </c>
@@ -3322,7 +3367,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>155</v>
       </c>
@@ -3338,8 +3383,11 @@
       <c r="E50" s="1" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H50" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>158</v>
       </c>
@@ -3356,7 +3404,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>161</v>
       </c>
@@ -3372,8 +3420,11 @@
       <c r="E52" s="1" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H52" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>164</v>
       </c>
@@ -3390,7 +3441,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>167</v>
       </c>
@@ -3407,7 +3458,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>170</v>
       </c>
@@ -3420,8 +3471,11 @@
       <c r="D55" s="1" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H55" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>173</v>
       </c>
@@ -3434,8 +3488,11 @@
       <c r="D56" s="1" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H56" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>176</v>
       </c>
@@ -3449,7 +3506,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>179</v>
       </c>
@@ -3463,7 +3520,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>182</v>
       </c>
@@ -3477,7 +3534,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>185</v>
       </c>
@@ -3491,7 +3548,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>188</v>
       </c>
@@ -3505,7 +3562,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>191</v>
       </c>
@@ -3519,7 +3576,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>194</v>
       </c>
@@ -3533,7 +3590,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>197</v>
       </c>
@@ -3596,6 +3653,9 @@
       </c>
       <c r="D67" s="1" t="s">
         <v>208</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56708731-47D0-4C38-B411-A7D48DF2E9DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B49F6EA-5137-4CF0-8671-561E11E4B10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3505,6 +3505,9 @@
       <c r="D57" s="1" t="s">
         <v>178</v>
       </c>
+      <c r="H57" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
@@ -4454,6 +4457,9 @@
       <c r="G110" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H110" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
@@ -4486,7 +4492,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>344</v>
       </c>
@@ -4500,7 +4506,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>347</v>
       </c>
@@ -4517,7 +4523,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>350</v>
       </c>
@@ -4537,7 +4543,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>353</v>
       </c>
@@ -4557,7 +4563,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>356</v>
       </c>
@@ -4571,7 +4577,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>358</v>
       </c>
@@ -4590,8 +4596,11 @@
       <c r="G118" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H118" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>361</v>
       </c>
@@ -4610,8 +4619,11 @@
       <c r="G119" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H119" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>364</v>
       </c>
@@ -4633,8 +4645,11 @@
       <c r="G120" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H120" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>367</v>
       </c>
@@ -4651,7 +4666,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>370</v>
       </c>
@@ -4668,7 +4683,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>373</v>
       </c>
@@ -4688,7 +4703,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>376</v>
       </c>
@@ -4702,7 +4717,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>379</v>
       </c>
@@ -4719,7 +4734,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>382</v>
       </c>
@@ -4742,7 +4757,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>385</v>
       </c>
@@ -4756,7 +4771,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>33</v>
       </c>
@@ -4809,6 +4824,9 @@
       <c r="G130" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H130" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
@@ -4829,6 +4847,9 @@
       <c r="G131" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H131" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
@@ -4880,6 +4901,9 @@
       <c r="G134" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H134" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
@@ -4917,6 +4941,9 @@
       <c r="G136" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H136" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
@@ -5147,6 +5174,9 @@
       <c r="G149" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H149" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
@@ -5164,6 +5194,9 @@
       <c r="G150" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H150" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
@@ -5181,6 +5214,9 @@
       <c r="G151" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H151" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
@@ -5466,6 +5502,9 @@
       <c r="D166" s="1" t="s">
         <v>501</v>
       </c>
+      <c r="H166" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
@@ -5480,6 +5519,9 @@
       <c r="D167" s="1" t="s">
         <v>504</v>
       </c>
+      <c r="H167" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
@@ -5598,6 +5640,9 @@
       </c>
       <c r="G174" s="1" t="s">
         <v>527</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B49F6EA-5137-4CF0-8671-561E11E4B10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B4470E-775F-4C29-A7DE-04F806699FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3133,6 +3133,9 @@
       <c r="D36" s="1" t="s">
         <v>117</v>
       </c>
+      <c r="H36" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
@@ -3147,6 +3150,9 @@
       <c r="D37" s="1" t="s">
         <v>119</v>
       </c>
+      <c r="H37" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
@@ -3161,6 +3167,9 @@
       <c r="D38" s="1" t="s">
         <v>121</v>
       </c>
+      <c r="H38" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
@@ -3175,6 +3184,9 @@
       <c r="D39" s="1" t="s">
         <v>124</v>
       </c>
+      <c r="H39" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
@@ -4491,6 +4503,9 @@
       <c r="D112" s="1" t="s">
         <v>343</v>
       </c>
+      <c r="H112" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
@@ -4505,6 +4520,9 @@
       <c r="D113" s="1" t="s">
         <v>346</v>
       </c>
+      <c r="H113" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
@@ -4756,6 +4774,9 @@
       <c r="G126" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H126" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
@@ -4884,6 +4905,9 @@
       <c r="G133" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H133" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
@@ -4961,6 +4985,9 @@
       <c r="G137" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H137" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
@@ -4995,6 +5022,9 @@
       <c r="G139" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H139" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
@@ -5049,6 +5079,9 @@
       <c r="E142" s="1" t="s">
         <v>431</v>
       </c>
+      <c r="H142" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
@@ -5069,6 +5102,9 @@
       <c r="F143" s="1" t="s">
         <v>434</v>
       </c>
+      <c r="H143" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
@@ -5086,6 +5122,9 @@
       <c r="F144" s="1" t="s">
         <v>437</v>
       </c>
+      <c r="H144" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
@@ -5157,6 +5196,9 @@
       <c r="E148" s="1" t="s">
         <v>449</v>
       </c>
+      <c r="H148" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
@@ -6166,7 +6208,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
         <v>619</v>
       </c>
@@ -6180,7 +6222,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
         <v>621</v>
       </c>
@@ -6194,7 +6236,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
         <v>623</v>
       </c>
@@ -6208,7 +6250,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
         <v>626</v>
       </c>
@@ -6222,7 +6264,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="1" t="s">
         <v>664</v>
       </c>
@@ -6236,7 +6278,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
         <v>665</v>
       </c>
@@ -6249,8 +6291,11 @@
       <c r="D214" s="1" t="s">
         <v>669</v>
       </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H214" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="1" t="s">
         <v>652</v>
       </c>
@@ -6263,8 +6308,11 @@
       <c r="D215" s="1" t="s">
         <v>660</v>
       </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H215" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="1" t="s">
         <v>653</v>
       </c>
@@ -6277,8 +6325,11 @@
       <c r="D216" s="1" t="s">
         <v>661</v>
       </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H216" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="1" t="s">
         <v>654</v>
       </c>
@@ -6291,8 +6342,11 @@
       <c r="D217" s="1" t="s">
         <v>662</v>
       </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H217" s="1" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
         <v>655</v>
       </c>
@@ -6304,6 +6358,9 @@
       </c>
       <c r="D218" s="1" t="s">
         <v>663</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B4470E-775F-4C29-A7DE-04F806699FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7668B3D3-F744-42B3-A278-79C4F6AD1663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2641,6 +2641,9 @@
       <c r="G9" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H9" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7668B3D3-F744-42B3-A278-79C4F6AD1663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6153324F-8778-4C72-A0FD-E3AC7FF9AB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1159" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="672">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2624,6 +2624,9 @@
       <c r="D8" s="1" t="s">
         <v>50</v>
       </c>
+      <c r="H8" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -2852,6 +2855,9 @@
       <c r="G20" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H20" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
@@ -2869,6 +2875,9 @@
       <c r="E21" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="H21" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
@@ -2886,6 +2895,9 @@
       <c r="E22" s="1" t="s">
         <v>82</v>
       </c>
+      <c r="H22" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
@@ -2903,6 +2915,9 @@
       <c r="E23" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="H23" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
@@ -2920,6 +2935,9 @@
       <c r="E24" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
@@ -3378,8 +3396,14 @@
       <c r="D49" s="1" t="s">
         <v>154</v>
       </c>
+      <c r="E49" s="1" t="s">
+        <v>154</v>
+      </c>
       <c r="G49" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
@@ -4492,6 +4516,9 @@
       <c r="G111" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H111" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
@@ -4543,6 +4570,9 @@
       <c r="G114" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H114" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
@@ -5008,6 +5038,9 @@
       <c r="E138" s="1" t="s">
         <v>419</v>
       </c>
+      <c r="H138" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
@@ -5148,6 +5181,9 @@
       <c r="F145" s="1" t="s">
         <v>440</v>
       </c>
+      <c r="H145" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
@@ -5165,6 +5201,9 @@
       <c r="F146" s="1" t="s">
         <v>443</v>
       </c>
+      <c r="H146" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
@@ -5603,6 +5642,9 @@
       </c>
       <c r="G169" s="1" t="s">
         <v>52</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6153324F-8778-4C72-A0FD-E3AC7FF9AB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611FE9E4-14C4-45DC-8EFC-07CDCA5DD78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="673">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2054,6 +2054,10 @@
   </si>
   <si>
     <t># 구현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>NORMAL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3237,10 +3241,13 @@
         <v>128</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>648</v>
+        <v>672</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>129</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -3282,6 +3289,9 @@
       <c r="G43" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H43" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
@@ -3322,6 +3332,9 @@
       <c r="G45" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="H45" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
@@ -3382,6 +3395,9 @@
       <c r="D48" s="1" t="s">
         <v>151</v>
       </c>
+      <c r="H48" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
@@ -3630,6 +3646,9 @@
       </c>
       <c r="D63" s="1" t="s">
         <v>196</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611FE9E4-14C4-45DC-8EFC-07CDCA5DD78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF90A45-6D05-4C94-99D0-1B4FC6F403E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="673">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2802,6 +2802,9 @@
       <c r="G17" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="H17" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
@@ -2822,6 +2825,9 @@
       <c r="G18" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="H18" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
@@ -2842,6 +2848,9 @@
       <c r="G19" s="1" t="s">
         <v>71</v>
       </c>
+      <c r="H19" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
@@ -4939,6 +4948,9 @@
       </c>
       <c r="E132" s="1" t="s">
         <v>401</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CF90A45-6D05-4C94-99D0-1B4FC6F403E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCC365F-881F-40F5-863B-01AA30383BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="673">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3504,6 +3504,9 @@
       <c r="E53" s="1" t="s">
         <v>166</v>
       </c>
+      <c r="H53" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
@@ -3586,6 +3589,9 @@
       <c r="D58" s="1" t="s">
         <v>181</v>
       </c>
+      <c r="H58" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
@@ -3600,6 +3606,9 @@
       <c r="E59" s="1" t="s">
         <v>184</v>
       </c>
+      <c r="H59" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
@@ -3614,6 +3623,9 @@
       <c r="D60" s="1" t="s">
         <v>187</v>
       </c>
+      <c r="H60" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
@@ -3628,6 +3640,9 @@
       <c r="E61" s="1" t="s">
         <v>190</v>
       </c>
+      <c r="H61" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
@@ -3642,6 +3657,9 @@
       <c r="D62" s="1" t="s">
         <v>193</v>
       </c>
+      <c r="H62" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
@@ -3679,6 +3697,9 @@
       <c r="F64" s="1" t="s">
         <v>199</v>
       </c>
+      <c r="H64" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
@@ -4869,6 +4890,9 @@
       <c r="G128" s="1" t="s">
         <v>389</v>
       </c>
+      <c r="H128" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
@@ -5008,6 +5032,9 @@
       </c>
       <c r="E135" s="1" t="s">
         <v>410</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFCC365F-881F-40F5-863B-01AA30383BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BDDBABE-0D5D-4B41-8F82-F110F686593E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="673">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="674">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2058,6 +2058,10 @@
   </si>
   <si>
     <t>NORMAL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/spell/자동보호.lua</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2666,7 +2670,10 @@
         <v>54</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>54</v>
+        <v>673</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -2685,6 +2692,9 @@
       <c r="E11" s="1" t="s">
         <v>56</v>
       </c>
+      <c r="H11" s="1" t="s">
+        <v>670</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
@@ -2781,6 +2791,9 @@
       </c>
       <c r="E16" s="1" t="s">
         <v>67</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>670</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1306C081-85A6-4503-86B3-578EC6B101E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9582AB-9460-4B37-A5AB-097FB58FEC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1489" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1030">
   <si>
     <t>server</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -116,9 +116,6 @@
     <t>1022</t>
   </si>
   <si>
-    <t>1024</t>
-  </si>
-  <si>
     <t>4001</t>
   </si>
   <si>
@@ -2265,9 +2262,6 @@
     <t>ON_CAST_1023</t>
   </si>
   <si>
-    <t>ON_CAST_1024</t>
-  </si>
-  <si>
     <t>ON_CAST_2001</t>
   </si>
   <si>
@@ -2847,286 +2841,287 @@
     <t>ON_CAST_4025</t>
   </si>
   <si>
+    <t>ON_CAST_4027</t>
+  </si>
+  <si>
+    <t>ON_CAST_4028</t>
+  </si>
+  <si>
+    <t>ON_CAST_4029</t>
+  </si>
+  <si>
+    <t>ON_CAST_4030</t>
+  </si>
+  <si>
+    <t>ON_CAST_4031</t>
+  </si>
+  <si>
+    <t>ON_CAST_4032</t>
+  </si>
+  <si>
+    <t>ON_CAST_4033</t>
+  </si>
+  <si>
+    <t>ON_CAST_4034</t>
+  </si>
+  <si>
+    <t>ON_CAST_4035</t>
+  </si>
+  <si>
+    <t>ON_CAST_4036</t>
+  </si>
+  <si>
+    <t>ON_CAST_4037</t>
+  </si>
+  <si>
+    <t>ON_CAST_4038</t>
+  </si>
+  <si>
+    <t>ON_CAST_4039</t>
+  </si>
+  <si>
+    <t>ON_CAST_4040</t>
+  </si>
+  <si>
+    <t>ON_CAST_4041</t>
+  </si>
+  <si>
+    <t>ON_CAST_4042</t>
+  </si>
+  <si>
+    <t>ON_CAST_5001</t>
+  </si>
+  <si>
+    <t>ON_CAST_5002</t>
+  </si>
+  <si>
+    <t>ON_CAST_5003</t>
+  </si>
+  <si>
+    <t>ON_CAST_5004</t>
+  </si>
+  <si>
+    <t>ON_CAST_5005</t>
+  </si>
+  <si>
+    <t>ON_CAST_5006</t>
+  </si>
+  <si>
+    <t>ON_CAST_5007</t>
+  </si>
+  <si>
+    <t>ON_CAST_5008</t>
+  </si>
+  <si>
+    <t>ON_CAST_5009</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6001</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6001</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6002</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6002</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6003</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6003</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6003</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6004</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6004</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6004</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6005</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6005</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6005</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6006</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6006</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6006</t>
+  </si>
+  <si>
+    <t>ON_CAST_6007</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6007</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6007</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6008</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6008</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6008</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6009</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6009</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6009</t>
+  </si>
+  <si>
+    <t>ON_CAST_6010</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6010</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6011</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6011</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6012</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6012</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6013</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6014</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6015</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6016</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6016</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6016</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6017</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6018</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6019</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6020</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6021</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6021</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6021</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6022</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6022</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6022</t>
+  </si>
+  <si>
+    <t>ON_BUFF_6023</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_6023</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_6023</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7001</t>
+  </si>
+  <si>
+    <t>ON_CAST_7002</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7003</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7004</t>
+  </si>
+  <si>
+    <t>ON_CAST_7005</t>
+  </si>
+  <si>
+    <t>ON_CAST_7006</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7007</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7008</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7009</t>
+  </si>
+  <si>
+    <t>ON_CAST_7010</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7011</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_7012</t>
+  </si>
+  <si>
+    <t>ON_CAST_7013</t>
+  </si>
+  <si>
+    <t>ON_CAST_10000</t>
+  </si>
+  <si>
+    <t>ON_CAST_10001</t>
+  </si>
+  <si>
+    <t>ON_CAST_10002</t>
+  </si>
+  <si>
+    <t>ON_CAST_10003</t>
+  </si>
+  <si>
+    <t>ON_CAST_10004</t>
+  </si>
+  <si>
     <t>ON_CAST_4026</t>
-  </si>
-  <si>
-    <t>ON_CAST_4027</t>
-  </si>
-  <si>
-    <t>ON_CAST_4028</t>
-  </si>
-  <si>
-    <t>ON_CAST_4029</t>
-  </si>
-  <si>
-    <t>ON_CAST_4030</t>
-  </si>
-  <si>
-    <t>ON_CAST_4031</t>
-  </si>
-  <si>
-    <t>ON_CAST_4032</t>
-  </si>
-  <si>
-    <t>ON_CAST_4033</t>
-  </si>
-  <si>
-    <t>ON_CAST_4034</t>
-  </si>
-  <si>
-    <t>ON_CAST_4035</t>
-  </si>
-  <si>
-    <t>ON_CAST_4036</t>
-  </si>
-  <si>
-    <t>ON_CAST_4037</t>
-  </si>
-  <si>
-    <t>ON_CAST_4038</t>
-  </si>
-  <si>
-    <t>ON_CAST_4039</t>
-  </si>
-  <si>
-    <t>ON_CAST_4040</t>
-  </si>
-  <si>
-    <t>ON_CAST_4041</t>
-  </si>
-  <si>
-    <t>ON_CAST_4042</t>
-  </si>
-  <si>
-    <t>ON_CAST_5001</t>
-  </si>
-  <si>
-    <t>ON_CAST_5002</t>
-  </si>
-  <si>
-    <t>ON_CAST_5003</t>
-  </si>
-  <si>
-    <t>ON_CAST_5004</t>
-  </si>
-  <si>
-    <t>ON_CAST_5005</t>
-  </si>
-  <si>
-    <t>ON_CAST_5006</t>
-  </si>
-  <si>
-    <t>ON_CAST_5007</t>
-  </si>
-  <si>
-    <t>ON_CAST_5008</t>
-  </si>
-  <si>
-    <t>ON_CAST_5009</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6001</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6001</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6002</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6002</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6003</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6003</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6003</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6004</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6004</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6004</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6005</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6005</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6005</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6006</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6006</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6006</t>
-  </si>
-  <si>
-    <t>ON_CAST_6007</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6007</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6007</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6008</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6008</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6008</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6009</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6009</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6009</t>
-  </si>
-  <si>
-    <t>ON_CAST_6010</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6010</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6011</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6011</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6012</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6012</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6013</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6014</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6015</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6016</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6016</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6016</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6017</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6018</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6019</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6020</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6021</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6021</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6021</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6022</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6022</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6022</t>
-  </si>
-  <si>
-    <t>ON_BUFF_6023</t>
-  </si>
-  <si>
-    <t>ON_UNBUFF_6023</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_6023</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7001</t>
-  </si>
-  <si>
-    <t>ON_CAST_7002</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7003</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7004</t>
-  </si>
-  <si>
-    <t>ON_CAST_7005</t>
-  </si>
-  <si>
-    <t>ON_CAST_7006</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7007</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7008</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7009</t>
-  </si>
-  <si>
-    <t>ON_CAST_7010</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7011</t>
-  </si>
-  <si>
-    <t>ON_CONCAST_7012</t>
-  </si>
-  <si>
-    <t>ON_CAST_7013</t>
-  </si>
-  <si>
-    <t>ON_CAST_10000</t>
-  </si>
-  <si>
-    <t>ON_CAST_10001</t>
-  </si>
-  <si>
-    <t>ON_CAST_10002</t>
-  </si>
-  <si>
-    <t>ON_CAST_10003</t>
-  </si>
-  <si>
-    <t>ON_CAST_10004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3189,7 +3184,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3205,7 +3200,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -3501,7 +3496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7A1E07-EEF2-4E86-80A0-A85D709C37E7}">
-  <dimension ref="A1:J219"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -3529,98 +3524,98 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>668</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>669</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>638</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>665</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>670</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>663</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>664</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>672</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -3628,22 +3623,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>678</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="J4" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -3651,22 +3646,22 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>37</v>
-      </c>
       <c r="J5" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -3674,22 +3669,22 @@
         <v>10</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="J6" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -3697,22 +3692,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>681</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="J7" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -3720,19 +3715,19 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -3743,19 +3738,19 @@
         <v>15</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>683</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="J9" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -3763,25 +3758,25 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E10" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>684</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="G10" s="1" t="s">
         <v>685</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>686</v>
-      </c>
       <c r="J10" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -3789,25 +3784,25 @@
         <v>12</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="E11" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>687</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="G11" s="1" t="s">
         <v>688</v>
       </c>
-      <c r="G11" s="1" t="s">
-        <v>689</v>
-      </c>
       <c r="J11" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -3815,22 +3810,22 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D12" s="1" t="s">
+      <c r="E12" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="I12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="J12" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -3838,22 +3833,22 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="E13" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -3861,22 +3856,22 @@
         <v>4</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="E14" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -3884,22 +3879,22 @@
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="E15" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -3907,54 +3902,54 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E16" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>694</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="G16" s="1" t="s">
         <v>695</v>
       </c>
-      <c r="G16" s="1" t="s">
-        <v>696</v>
-      </c>
       <c r="J16" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C17" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>699</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="J17" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
@@ -3962,28 +3957,28 @@
         <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="E18" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>700</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>701</v>
       </c>
-      <c r="G18" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="I18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -3991,28 +3986,28 @@
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="E19" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>703</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>704</v>
       </c>
-      <c r="G19" s="1" t="s">
-        <v>705</v>
-      </c>
       <c r="I19" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -4020,22 +4015,22 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E20" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -4043,77 +4038,77 @@
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="E21" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>708</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>709</v>
-      </c>
       <c r="J21" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="C22" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>77</v>
-      </c>
       <c r="E22" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F22" s="1" t="s">
         <v>710</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>711</v>
       </c>
-      <c r="G22" s="1" t="s">
-        <v>712</v>
-      </c>
       <c r="J22" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="C23" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E23" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>713</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="G23" s="1" t="s">
         <v>714</v>
       </c>
-      <c r="G23" s="1" t="s">
-        <v>715</v>
-      </c>
       <c r="J23" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
@@ -4121,25 +4116,25 @@
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
       <c r="E24" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>716</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="G24" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="G24" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="J24" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
@@ -4147,25 +4142,25 @@
         <v>20</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="E25" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>720</v>
       </c>
-      <c r="G25" s="1" t="s">
-        <v>721</v>
-      </c>
       <c r="J25" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
@@ -4173,103 +4168,103 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>86</v>
-      </c>
       <c r="E26" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="F26" s="1" t="s">
         <v>722</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="G26" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="J26" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="C27" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>89</v>
-      </c>
       <c r="E27" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="F27" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="G27" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>727</v>
-      </c>
       <c r="J27" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="C28" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D28" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="E28" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F28" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="J28" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="E29" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="G29" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="G29" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="J29" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
@@ -4277,19 +4272,19 @@
         <v>23</v>
       </c>
       <c r="B30" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="E30" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
@@ -4297,19 +4292,19 @@
         <v>24</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="E31" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
@@ -4317,79 +4312,79 @@
         <v>25</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="E33" s="1" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="C34" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E34" s="1" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="C35" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D35" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="E35" s="1" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
@@ -4397,19 +4392,19 @@
         <v>26</v>
       </c>
       <c r="B36" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D36" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="E36" s="1" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
@@ -4417,19 +4412,19 @@
         <v>27</v>
       </c>
       <c r="B37" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>114</v>
-      </c>
       <c r="E37" s="1" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
@@ -4437,2647 +4432,2644 @@
         <v>28</v>
       </c>
       <c r="B38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="E38" s="1" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="C39" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>47</v>
+        <v>743</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E41" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="F41" s="1" t="s">
         <v>745</v>
       </c>
+      <c r="G41" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="I41" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="J41" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>746</v>
-      </c>
-      <c r="F42" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="I42" s="1" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>749</v>
       </c>
+      <c r="G43" s="1" t="s">
+        <v>750</v>
+      </c>
       <c r="I43" s="1" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="F44" s="1" t="s">
         <v>751</v>
       </c>
-      <c r="G44" s="1" t="s">
-        <v>752</v>
-      </c>
       <c r="I44" s="1" t="s">
-        <v>128</v>
+        <v>46</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E45" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="F45" s="1" t="s">
         <v>753</v>
       </c>
+      <c r="G45" s="1" t="s">
+        <v>754</v>
+      </c>
       <c r="I45" s="1" t="s">
-        <v>47</v>
+        <v>127</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>757</v>
-      </c>
-      <c r="F47" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="G47" s="1" t="s">
-        <v>759</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="J47" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="F48" s="1" t="s">
         <v>760</v>
       </c>
+      <c r="G48" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J48" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>763</v>
-      </c>
-      <c r="I49" s="1" t="s">
-        <v>47</v>
+        <v>764</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>766</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>660</v>
+        <v>767</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>769</v>
+        <v>770</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>775</v>
-      </c>
-      <c r="J53" s="1" t="s">
-        <v>660</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>776</v>
-      </c>
-      <c r="F54" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="G54" s="1" t="s">
-        <v>778</v>
+      <c r="J54" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E58" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="G58" s="1" t="s">
         <v>782</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="F59" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="E59" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="J59" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E60" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>785</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F61" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="G61" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="J61" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="F63" s="1" t="s">
         <v>789</v>
       </c>
+      <c r="G63" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>791</v>
+      </c>
       <c r="J63" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="J64" s="1" t="s">
-        <v>660</v>
+        <v>794</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="F65" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="G65" s="1" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="F67" s="1" t="s">
         <v>798</v>
       </c>
+      <c r="G67" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J67" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>799</v>
-      </c>
-      <c r="F68" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="G68" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="I68" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="I74" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J74" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J76" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J77" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J78" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J79" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J80" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="I81" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J81" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="I82" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J82" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J83" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J84" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J85" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J86" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J87" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="I88" s="1" t="s">
-        <v>47</v>
+        <v>820</v>
       </c>
       <c r="J88" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="J89" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="J90" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="J91" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="J92" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="J93" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J94" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J95" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J96" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J97" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J98" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J99" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J100" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="J101" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="J102" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="J103" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="J104" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="J105" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="J106" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="J107" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C108" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>841</v>
-      </c>
-      <c r="J108" s="1" t="s">
-        <v>660</v>
+        <v>840</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="I109" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="I110" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J110" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B111" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>844</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>47</v>
+        <v>843</v>
       </c>
       <c r="J111" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B112" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="J112" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>846</v>
+        <v>845</v>
+      </c>
+      <c r="I113" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J113" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E114" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="F114" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="I114" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>660</v>
+      <c r="G114" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>849</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B115" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>848</v>
-      </c>
-      <c r="F115" s="1" t="s">
-        <v>849</v>
-      </c>
-      <c r="G115" s="1" t="s">
         <v>850</v>
       </c>
       <c r="H115" s="1" t="s">
         <v>851</v>
       </c>
+      <c r="I115" s="1" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B116" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="E116" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="H116" s="1" t="s">
         <v>852</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B117" s="1" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>622</v>
-      </c>
-      <c r="H117" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="F117" s="1" t="s">
         <v>854</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J117" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B118" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="I118" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J118" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B119" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="G119" s="1" t="s">
-        <v>860</v>
+        <v>861</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>862</v>
       </c>
       <c r="I119" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J119" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B120" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>862</v>
-      </c>
-      <c r="G120" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>864</v>
-      </c>
       <c r="I120" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J120" s="1" t="s">
-        <v>660</v>
+        <v>46</v>
       </c>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B121" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E121" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="F121" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="I121" s="1" t="s">
-        <v>47</v>
+      <c r="G121" s="1" t="s">
+        <v>866</v>
       </c>
     </row>
     <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B122" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>868</v>
+        <v>869</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>870</v>
       </c>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B123" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>869</v>
+        <v>372</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>871</v>
-      </c>
-      <c r="H123" s="1" t="s">
         <v>872</v>
       </c>
     </row>
     <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B124" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>873</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C125" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>877</v>
+        <v>878</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="I125" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J125" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="F126" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="G126" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="H126" s="1" t="s">
         <v>880</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J126" s="1" t="s">
-        <v>660</v>
       </c>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
-        <v>380</v>
+        <v>29</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>381</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>623</v>
-      </c>
-      <c r="H127" s="1" t="s">
-        <v>882</v>
+        <v>382</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="I127" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J127" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
-        <v>30</v>
+        <v>384</v>
       </c>
       <c r="B128" s="1" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C128" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="I128" s="1" t="s">
-        <v>384</v>
+        <v>882</v>
       </c>
       <c r="J128" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B129" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C129" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E129" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="F129" s="1" t="s">
         <v>884</v>
       </c>
+      <c r="G129" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="I129" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="J129" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="I130" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J130" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>890</v>
-      </c>
-      <c r="I131" s="1" t="s">
-        <v>47</v>
+        <v>891</v>
       </c>
       <c r="J131" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B132" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C132" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>891</v>
-      </c>
-      <c r="F132" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="G132" s="1" t="s">
-        <v>893</v>
+      <c r="I132" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J132" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B133" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="I133" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J133" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B134" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E134" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="I134" s="1" t="s">
-        <v>47</v>
+      <c r="G134" s="1" t="s">
+        <v>896</v>
       </c>
       <c r="J134" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C135" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J135" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>899</v>
-      </c>
-      <c r="F136" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="G136" s="1" t="s">
-        <v>901</v>
-      </c>
       <c r="I136" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J136" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="F137" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="I137" s="1" t="s">
-        <v>47</v>
+      <c r="G137" s="1" t="s">
+        <v>903</v>
       </c>
       <c r="J137" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B138" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C138" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>903</v>
-      </c>
-      <c r="F138" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="G138" s="1" t="s">
-        <v>905</v>
+      <c r="I138" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J138" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B139" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E139" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="F139" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="I139" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J139" s="1" t="s">
-        <v>660</v>
+      <c r="G139" s="1" t="s">
+        <v>907</v>
       </c>
     </row>
     <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B140" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C140" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>907</v>
-      </c>
-      <c r="F140" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="G140" s="1" t="s">
-        <v>909</v>
+      <c r="I140" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B141" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E141" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="F141" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="I141" s="1" t="s">
-        <v>47</v>
+      <c r="G141" s="1" t="s">
+        <v>911</v>
       </c>
       <c r="J141" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B142" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>915</v>
       </c>
       <c r="J142" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B143" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>914</v>
+        <v>431</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="H143" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="J143" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B144" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>919</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="E145" s="1" t="s">
-        <v>921</v>
+        <v>437</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="J145" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B146" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
+      </c>
+      <c r="E146" s="1" t="s">
+        <v>926</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="J146" s="1" t="s">
-        <v>660</v>
+        <v>928</v>
       </c>
     </row>
     <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>930</v>
+        <v>931</v>
+      </c>
+      <c r="J147" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B148" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C148" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>931</v>
-      </c>
-      <c r="F148" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="G148" s="1" t="s">
-        <v>933</v>
+      <c r="I148" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J148" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="I149" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J149" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B150" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="I150" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J150" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B151" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>936</v>
-      </c>
-      <c r="I151" s="1" t="s">
-        <v>47</v>
+        <v>935</v>
       </c>
       <c r="J151" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>455</v>
+        <v>119</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>456</v>
+        <v>120</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>937</v>
+        <v>1029</v>
       </c>
       <c r="J152" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="153" spans="1:10" x14ac:dyDescent="0.3">
@@ -7085,609 +7077,612 @@
         <v>457</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>120</v>
+        <v>458</v>
       </c>
       <c r="C153" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>121</v>
+        <v>459</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>938</v>
+        <v>936</v>
+      </c>
+      <c r="I153" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J153" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="I154" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J154" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>940</v>
-      </c>
-      <c r="I155" s="1" t="s">
-        <v>47</v>
+        <v>938</v>
       </c>
       <c r="J155" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C156" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>941</v>
+        <v>939</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J156" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="I157" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J157" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="I158" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J158" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="I159" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J159" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="I160" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J160" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="I161" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J161" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="I162" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J162" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="I163" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J163" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="I164" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J164" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="I165" s="1" t="s">
-        <v>47</v>
+        <v>948</v>
       </c>
       <c r="J165" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="J166" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C167" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>952</v>
+        <v>950</v>
+      </c>
+      <c r="I167" s="1" t="s">
+        <v>46</v>
       </c>
       <c r="J167" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="I168" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J168" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="I169" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J169" s="1" t="s">
-        <v>660</v>
+        <v>42</v>
       </c>
     </row>
     <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="I170" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C171" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>956</v>
-      </c>
-      <c r="I171" s="1" t="s">
-        <v>40</v>
+        <v>954</v>
       </c>
     </row>
     <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>957</v>
+        <v>955</v>
+      </c>
+      <c r="I172" s="1" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="I173" s="1" t="s">
-        <v>518</v>
+        <v>521</v>
+      </c>
+      <c r="J173" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="I174" s="1" t="s">
-        <v>522</v>
+        <v>53</v>
       </c>
       <c r="J174" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="I175" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="J175" s="1" t="s">
-        <v>660</v>
+        <v>46</v>
       </c>
     </row>
     <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>961</v>
-      </c>
-      <c r="I176" s="1" t="s">
-        <v>47</v>
+        <v>959</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="1" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="1" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E178" s="1" t="s">
-        <v>963</v>
+        <v>536</v>
+      </c>
+      <c r="F178" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>962</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="1" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="F179" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="G179" s="1" t="s">
         <v>964</v>
-      </c>
-      <c r="G179" s="1" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="1" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="F180" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="G180" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="G180" s="1" t="s">
+      <c r="H180" s="1" t="s">
         <v>967</v>
       </c>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="1" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>543</v>
+        <v>665</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>968</v>
@@ -7701,16 +7696,16 @@
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>666</v>
+        <v>547</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>971</v>
@@ -7724,16 +7719,16 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="1" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>974</v>
@@ -7747,62 +7742,62 @@
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="1" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>551</v>
+        <v>553</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>977</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="H184" s="1" t="s">
         <v>979</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="1" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E185" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="F185" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="F185" s="1" t="s">
+      <c r="G185" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="G185" s="1" t="s">
+      <c r="H185" s="1" t="s">
         <v>982</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="1" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>983</v>
@@ -7816,133 +7811,133 @@
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="1" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="F187" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="G187" s="1" t="s">
+      <c r="H187" s="1" t="s">
         <v>987</v>
-      </c>
-      <c r="H187" s="1" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="E188" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="G188" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="H188" s="1" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="1" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="F189" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="G189" s="1" t="s">
         <v>991</v>
-      </c>
-      <c r="G189" s="1" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="1" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>993</v>
-      </c>
-      <c r="G190" s="1" t="s">
-        <v>994</v>
+        <v>623</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>992</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B191" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>624</v>
       </c>
       <c r="H191" s="1" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B192" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>625</v>
       </c>
       <c r="H192" s="1" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B193" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>626</v>
+        <v>577</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>996</v>
       </c>
       <c r="H193" s="1" t="s">
         <v>997</v>
@@ -7950,90 +7945,90 @@
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="1" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="F194" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="H194" s="1" t="s">
         <v>998</v>
-      </c>
-      <c r="G194" s="1" t="s">
-        <v>999</v>
-      </c>
-      <c r="H194" s="1" t="s">
-        <v>1000</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B195" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>627</v>
       </c>
       <c r="H195" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>628</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B197" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>629</v>
       </c>
       <c r="H197" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>630</v>
+        <v>588</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>1003</v>
       </c>
       <c r="H198" s="1" t="s">
         <v>1004</v>
@@ -8041,16 +8036,16 @@
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>1005</v>
@@ -8064,16 +8059,16 @@
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="1" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>1008</v>
@@ -8087,212 +8082,206 @@
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>595</v>
-      </c>
-      <c r="F201" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="H201" s="1" t="s">
         <v>1011</v>
-      </c>
-      <c r="G201" s="1" t="s">
-        <v>1012</v>
-      </c>
-      <c r="H201" s="1" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="1" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B202" s="1" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>631</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>1014</v>
+        <v>599</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>1012</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="1" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B203" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>600</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>1015</v>
+        <v>631</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>1013</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="1" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B204" s="1" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>632</v>
       </c>
       <c r="H204" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="1" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B205" s="1" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>633</v>
-      </c>
-      <c r="H205" s="1" t="s">
-        <v>1017</v>
+        <v>606</v>
+      </c>
+      <c r="E205" s="1" t="s">
+        <v>1015</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="1" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B206" s="1" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="1" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B207" s="1" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C207" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>610</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>1019</v>
+        <v>633</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>1017</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="1" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B208" s="1" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>634</v>
       </c>
       <c r="H208" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B209" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>635</v>
       </c>
       <c r="H209" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B210" s="1" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>636</v>
-      </c>
-      <c r="H210" s="1" t="s">
-        <v>1022</v>
+        <v>618</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>1020</v>
       </c>
     </row>
     <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B211" s="1" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>1023</v>
+        <v>636</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>1021</v>
       </c>
     </row>
     <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1" t="s">
-        <v>620</v>
+        <v>672</v>
       </c>
       <c r="B212" s="1" t="s">
-        <v>621</v>
+        <v>655</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="H212" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="213" spans="1:10" x14ac:dyDescent="0.3">
@@ -8308,28 +8297,31 @@
       <c r="D213" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="H213" s="1" t="s">
-        <v>1025</v>
+      <c r="E213" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="J213" s="1" t="s">
+        <v>659</v>
       </c>
     </row>
     <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1" t="s">
-        <v>674</v>
+        <v>643</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>657</v>
+        <v>647</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>659</v>
+        <v>651</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="J214" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="215" spans="1:10" x14ac:dyDescent="0.3">
@@ -8340,16 +8332,16 @@
         <v>648</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>652</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J215" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="216" spans="1:10" x14ac:dyDescent="0.3">
@@ -8360,16 +8352,16 @@
         <v>649</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>653</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="J216" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="217" spans="1:10" x14ac:dyDescent="0.3">
@@ -8380,56 +8372,36 @@
         <v>650</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>654</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="J217" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>651</v>
+        <v>675</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="J218" s="1" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A219" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="B219" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="D219" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\fb\resources\table\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9582AB-9460-4B37-A5AB-097FB58FEC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91F49F-E44A-4417-9175-3396BC99589A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-135" windowWidth="38640" windowHeight="21120" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2169" uniqueCount="1493">
   <si>
     <t>server</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3122,6 +3122,1396 @@
   <si>
     <t>ON_CAST_4026</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>의태시약</t>
+  </si>
+  <si>
+    <t>scripts/spell/의태시약.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_14</t>
+  </si>
+  <si>
+    <t>ON_BUFF_14</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">대상은? </t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>의태시약10</t>
+  </si>
+  <si>
+    <t>scripts/spell/의태시약10.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_15</t>
+  </si>
+  <si>
+    <t>ON_BUFF_15</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_15</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>시약보호</t>
+  </si>
+  <si>
+    <t>scripts/spell/시약보호.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_17</t>
+  </si>
+  <si>
+    <t>ON_BUFF_17</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>시약무장</t>
+  </si>
+  <si>
+    <t>scripts/spell/시약무장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_18</t>
+  </si>
+  <si>
+    <t>ON_BUFF_18</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_18</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>용의제일주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제일주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_21</t>
+  </si>
+  <si>
+    <t>ON_BUFF_21</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>용의제이주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제이주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_22</t>
+  </si>
+  <si>
+    <t>ON_BUFF_22</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>용의제삼주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제삼주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_23</t>
+  </si>
+  <si>
+    <t>ON_BUFF_23</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>용의제사주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제사주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_24</t>
+  </si>
+  <si>
+    <t>ON_BUFF_24</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>용의제오주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제오주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_25</t>
+  </si>
+  <si>
+    <t>ON_BUFF_25</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_25</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>용의제육주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제육주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_26</t>
+  </si>
+  <si>
+    <t>ON_BUFF_26</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>용의제칠주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제칠주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_27</t>
+  </si>
+  <si>
+    <t>ON_BUFF_27</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_27</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>용의제팔주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제팔주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_28</t>
+  </si>
+  <si>
+    <t>ON_BUFF_28</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_28</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>용의제구주</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제구주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_29</t>
+  </si>
+  <si>
+    <t>ON_BUFF_29</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_29</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>용의제일노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제일노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_31</t>
+  </si>
+  <si>
+    <t>ON_BUFF_31</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_31</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>용의제이노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제이노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_32</t>
+  </si>
+  <si>
+    <t>ON_BUFF_32</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_32</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>용의제삼노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제삼노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_33</t>
+  </si>
+  <si>
+    <t>ON_BUFF_33</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_33</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>용의제사노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제사노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_34</t>
+  </si>
+  <si>
+    <t>ON_BUFF_34</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_34</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>용의제오노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제오노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_35</t>
+  </si>
+  <si>
+    <t>ON_BUFF_35</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_35</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>용의제육노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제육노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_36</t>
+  </si>
+  <si>
+    <t>ON_BUFF_36</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_36</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>용의제칠노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제칠노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_37</t>
+  </si>
+  <si>
+    <t>ON_BUFF_37</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_37</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>용의제팔노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제팔노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_38</t>
+  </si>
+  <si>
+    <t>ON_BUFF_38</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_38</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>용의제구노</t>
+  </si>
+  <si>
+    <t>scripts/spell/용의제구노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_39</t>
+  </si>
+  <si>
+    <t>ON_BUFF_39</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_39</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>영후의저주</t>
+  </si>
+  <si>
+    <t>scripts/spell/영후의저주.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_50</t>
+  </si>
+  <si>
+    <t>ON_BUFF_50</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_50</t>
+  </si>
+  <si>
+    <t>53</t>
+  </si>
+  <si>
+    <t>반짝반짝</t>
+  </si>
+  <si>
+    <t>scripts/spell/반짝반짝.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_53</t>
+  </si>
+  <si>
+    <t>ON_BUFF_53</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_53</t>
+  </si>
+  <si>
+    <t>59</t>
+  </si>
+  <si>
+    <t>풍령의분노</t>
+  </si>
+  <si>
+    <t>scripts/spell/풍령의분노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_59</t>
+  </si>
+  <si>
+    <t>ON_BUFF_59</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_59</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>지령의분노</t>
+  </si>
+  <si>
+    <t>scripts/spell/지령의분노.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_60</t>
+  </si>
+  <si>
+    <t>ON_BUFF_60</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_60</t>
+  </si>
+  <si>
+    <t>61</t>
+  </si>
+  <si>
+    <t>늪의주박</t>
+  </si>
+  <si>
+    <t>scripts/spell/늪의주박.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_61</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>늪의주박술</t>
+  </si>
+  <si>
+    <t>scripts/spell/늪의주박술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_62</t>
+  </si>
+  <si>
+    <t>ON_BUFF_62</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_62</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_62</t>
+  </si>
+  <si>
+    <t>귀문진원</t>
+  </si>
+  <si>
+    <t>scripts/spell/귀문진원.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_68</t>
+  </si>
+  <si>
+    <t>ON_BUFF_68</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_68</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_68</t>
+  </si>
+  <si>
+    <t>빛나는연등</t>
+  </si>
+  <si>
+    <t>scripts/spell/빛나는연등.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_69</t>
+  </si>
+  <si>
+    <t>ON_BUFF_69</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_69</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_69</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>유저조사</t>
+  </si>
+  <si>
+    <t>scripts/spell/유저조사.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_90</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>일성백열장</t>
+  </si>
+  <si>
+    <t>scripts/spell/일성백열장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>이성백열장</t>
+  </si>
+  <si>
+    <t>scripts/spell/이성백열장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>삼성백열장</t>
+  </si>
+  <si>
+    <t>scripts/spell/삼성백열장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_105</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>사성백열장</t>
+  </si>
+  <si>
+    <t>scripts/spell/사성백열장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_106</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>오성백열장</t>
+  </si>
+  <si>
+    <t>scripts/spell/오성백열장.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_107</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_113</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>일성금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/일성금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_114</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>이성금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/이성금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_115</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>삼성금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/삼성금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_116</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>사성금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/사성금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_117</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>오성금강퇴</t>
+  </si>
+  <si>
+    <t>scripts/spell/오성금강퇴.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_118</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_119</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>일성선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/일성선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_120</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>이성선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/이성선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_121</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>삼성선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/삼성선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_122</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>사성선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/사성선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_123</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>오성선풍각</t>
+  </si>
+  <si>
+    <t>scripts/spell/오성선풍각.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_124</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>소림경수둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/소림경수둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_126</t>
+  </si>
+  <si>
+    <t>ON_BUFF_126</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_126</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">변신할 동물은? </t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>소림천구둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/소림천구둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_127</t>
+  </si>
+  <si>
+    <t>ON_BUFF_127</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_127</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_127</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>소림후둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/소림후둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_128</t>
+  </si>
+  <si>
+    <t>ON_BUFF_128</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_128</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_128</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>소림강시둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/소림강시둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_129</t>
+  </si>
+  <si>
+    <t>ON_BUFF_129</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_129</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_129</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>인어장군둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/인어장군둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_130</t>
+  </si>
+  <si>
+    <t>ON_BUFF_130</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_130</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_130</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>상어장군둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/상어장군둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_131</t>
+  </si>
+  <si>
+    <t>ON_BUFF_131</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_131</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_131</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>해파리장군둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/해파리장군둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_132</t>
+  </si>
+  <si>
+    <t>ON_BUFF_132</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_132</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_132</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>마려둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/마려둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_133</t>
+  </si>
+  <si>
+    <t>ON_BUFF_133</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_133</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_133</t>
+  </si>
+  <si>
+    <t>134</t>
+  </si>
+  <si>
+    <t>철거인둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/철거인둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_134</t>
+  </si>
+  <si>
+    <t>ON_BUFF_134</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_134</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_134</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>해골왕둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/해골왕둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_135</t>
+  </si>
+  <si>
+    <t>ON_BUFF_135</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_135</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_135</t>
+  </si>
+  <si>
+    <t>136</t>
+  </si>
+  <si>
+    <t>운랑둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/운랑둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_136</t>
+  </si>
+  <si>
+    <t>ON_BUFF_136</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_136</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_136</t>
+  </si>
+  <si>
+    <t>137</t>
+  </si>
+  <si>
+    <t>풍석둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/풍석둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_137</t>
+  </si>
+  <si>
+    <t>ON_BUFF_137</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_137</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_137</t>
+  </si>
+  <si>
+    <t>138</t>
+  </si>
+  <si>
+    <t>마계천신둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/마계천신둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_138</t>
+  </si>
+  <si>
+    <t>ON_BUFF_138</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_138</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_138</t>
+  </si>
+  <si>
+    <t>139</t>
+  </si>
+  <si>
+    <t>불의천신둔갑술</t>
+  </si>
+  <si>
+    <t>scripts/spell/불의천신둔갑술.lua</t>
+  </si>
+  <si>
+    <t>ON_CAST_139</t>
+  </si>
+  <si>
+    <t>ON_BUFF_139</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_139</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_139</t>
+  </si>
+  <si>
+    <t>용마제일격</t>
+  </si>
+  <si>
+    <t>용마제이격</t>
+  </si>
+  <si>
+    <t>용마제삼격</t>
+  </si>
+  <si>
+    <t>용마제사격</t>
+  </si>
+  <si>
+    <t>용마제오격</t>
+  </si>
+  <si>
+    <t>용마제육격</t>
+  </si>
+  <si>
+    <t>용마제칠격</t>
+  </si>
+  <si>
+    <t>용마제팔격</t>
+  </si>
+  <si>
+    <t>용마제구격</t>
+  </si>
+  <si>
+    <t>용천제일격</t>
+  </si>
+  <si>
+    <t>용천제이격</t>
+  </si>
+  <si>
+    <t>용천제삼격</t>
+  </si>
+  <si>
+    <t>용천제사격</t>
+  </si>
+  <si>
+    <t>용천제오격</t>
+  </si>
+  <si>
+    <t>용천제육격</t>
+  </si>
+  <si>
+    <t>용천제칠격</t>
+  </si>
+  <si>
+    <t>용천제팔격</t>
+  </si>
+  <si>
+    <t>용천제구격</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>49</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>54</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>58</t>
+  </si>
+  <si>
+    <t>63</t>
+  </si>
+  <si>
+    <t>64</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_30</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_40</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_41</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_42</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_43</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_44</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_45</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_46</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_47</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_48</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_49</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_51</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_52</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_54</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_55</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_56</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_57</t>
+  </si>
+  <si>
+    <t>ON_UNBUFF_58</t>
+  </si>
+  <si>
+    <t>ON_BUFF_30</t>
+  </si>
+  <si>
+    <t>ON_BUFF_40</t>
+  </si>
+  <si>
+    <t>ON_BUFF_41</t>
+  </si>
+  <si>
+    <t>ON_BUFF_42</t>
+  </si>
+  <si>
+    <t>ON_BUFF_43</t>
+  </si>
+  <si>
+    <t>ON_BUFF_44</t>
+  </si>
+  <si>
+    <t>ON_BUFF_45</t>
+  </si>
+  <si>
+    <t>ON_BUFF_46</t>
+  </si>
+  <si>
+    <t>ON_BUFF_47</t>
+  </si>
+  <si>
+    <t>ON_BUFF_48</t>
+  </si>
+  <si>
+    <t>ON_BUFF_49</t>
+  </si>
+  <si>
+    <t>ON_BUFF_51</t>
+  </si>
+  <si>
+    <t>ON_BUFF_52</t>
+  </si>
+  <si>
+    <t>ON_BUFF_54</t>
+  </si>
+  <si>
+    <t>ON_BUFF_55</t>
+  </si>
+  <si>
+    <t>ON_BUFF_56</t>
+  </si>
+  <si>
+    <t>ON_BUFF_57</t>
+  </si>
+  <si>
+    <t>ON_BUFF_58</t>
+  </si>
+  <si>
+    <t>ON_CONCAST_58</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ON_CAST_30</t>
+  </si>
+  <si>
+    <t>ON_CAST_40</t>
+  </si>
+  <si>
+    <t>ON_CAST_41</t>
+  </si>
+  <si>
+    <t>ON_CAST_42</t>
+  </si>
+  <si>
+    <t>ON_CAST_43</t>
+  </si>
+  <si>
+    <t>ON_CAST_44</t>
+  </si>
+  <si>
+    <t>ON_CAST_45</t>
+  </si>
+  <si>
+    <t>ON_CAST_46</t>
+  </si>
+  <si>
+    <t>ON_CAST_47</t>
+  </si>
+  <si>
+    <t>ON_CAST_48</t>
+  </si>
+  <si>
+    <t>ON_CAST_49</t>
+  </si>
+  <si>
+    <t>ON_CAST_51</t>
+  </si>
+  <si>
+    <t>ON_CAST_52</t>
+  </si>
+  <si>
+    <t>ON_CAST_54</t>
+  </si>
+  <si>
+    <t>ON_CAST_55</t>
+  </si>
+  <si>
+    <t>ON_CAST_56</t>
+  </si>
+  <si>
+    <t>ON_CAST_57</t>
+  </si>
+  <si>
+    <t>ON_CAST_58</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제일격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제이격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제삼격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제사격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제오격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제육격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제칠격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제팔격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용마제구격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제일격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제이격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제삼격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제사격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제오격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제육격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제칠격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제팔격.lua</t>
+  </si>
+  <si>
+    <t>scripts/spell/용천제구격.lua</t>
   </si>
 </sst>
 </file>
@@ -3184,7 +4574,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3200,7 +4590,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -3496,7 +4886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7A1E07-EEF2-4E86-80A0-A85D709C37E7}">
-  <dimension ref="A1:J218"/>
+  <dimension ref="A1:J298"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
@@ -8404,6 +9794,2227 @@
         <v>659</v>
       </c>
     </row>
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A219" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F219" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I219" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J219" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A220" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E220" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F220" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I220" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J220" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A221" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E221" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="F221" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I221" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J221" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A222" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E222" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F222" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I222" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J222" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A223" s="1" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E223" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F223" s="1" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G223" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I223" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J223" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A224" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E224" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F224" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G224" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="I224" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J224" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A225" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="E225" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F225" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="G225" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="I225" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J225" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A226" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>1478</v>
+      </c>
+      <c r="E226" s="1" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F226" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G226" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="I226" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J226" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A227" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E227" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F227" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G227" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="I227" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J227" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A228" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E228" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F228" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G228" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="I228" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J228" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A229" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E229" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F229" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="G229" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="I229" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J229" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A230" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E230" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F230" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="G230" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="I230" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J230" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A231" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E231" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F231" s="1" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G231" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I231" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J231" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A232" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E232" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="F232" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G232" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="I232" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J232" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A233" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E233" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F233" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G233" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="I233" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J233" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A234" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E234" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F234" s="1" t="s">
+        <v>1120</v>
+      </c>
+      <c r="G234" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I234" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J234" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A235" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>1487</v>
+      </c>
+      <c r="E235" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F235" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G235" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="I235" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J235" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A236" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E236" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F236" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="G236" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="I236" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J236" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A237" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E237" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F237" s="1" t="s">
+        <v>1138</v>
+      </c>
+      <c r="G237" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="I237" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J237" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A238" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E238" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F238" s="1" t="s">
+        <v>1144</v>
+      </c>
+      <c r="G238" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="I238" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J238" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A239" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>1491</v>
+      </c>
+      <c r="E239" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F239" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G239" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="I239" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J239" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A240" s="1" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E240" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F240" s="1" t="s">
+        <v>1156</v>
+      </c>
+      <c r="G240" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="I240" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J240" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A241" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E241" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F241" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G241" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="I241" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J241" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A242" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E242" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="F242" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G242" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I242" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J242" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A243" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B243" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D243" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E243" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F243" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G243" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="I243" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J243" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A244" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B244" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D244" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E244" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="F244" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="G244" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="I244" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J244" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A245" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E245" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F245" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="G245" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I245" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J245" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A246" s="1" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D246" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E246" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="F246" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="G246" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I246" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J246" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A247" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D247" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F247" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G247" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="I247" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J247" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A248" s="1" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D248" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E248" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F248" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="G248" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I248" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J248" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A249" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E249" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="F249" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="G249" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="I249" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J249" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A250" s="1" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D250" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E250" s="1" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F250" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G250" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="I250" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J250" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A251" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D251" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E251" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F251" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="G251" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="I251" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J251" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A252" s="1" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B252" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C252" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E252" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F252" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G252" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="I252" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J252" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A253" s="1" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B253" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E253" s="1" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F253" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G253" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="I253" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J253" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A254" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B254" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D254" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E254" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F254" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G254" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="I254" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J254" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A255" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B255" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D255" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E255" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F255" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="G255" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="I255" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J255" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A256" s="1" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B256" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D256" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E256" s="1" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F256" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="G256" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="I256" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J256" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A257" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B257" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E257" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F257" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G257" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I257" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J257" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A258" s="1" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B258" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E258" s="1" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F258" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="G258" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="I258" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J258" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A259" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B259" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D259" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E259" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="F259" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="G259" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J259" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A260" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B260" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D260" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="E260" s="1" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F260" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G260" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="H260" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I260" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J260" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A261" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F261" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="G261" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="J261" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A262" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F262" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="G262" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J262" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A263" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B263" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D263" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E263" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="I263" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J263" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A264" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F264" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="G264" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="H264" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="J264" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A265" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B265" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="G265" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="H265" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="J265" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A266" s="1" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B266" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G266" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="H266" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="J266" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A267" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B267" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D267" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="E267" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="J267" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A268" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B268" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D268" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E268" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I268" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J268" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A269" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B269" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D269" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E269" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="I269" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J269" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A270" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B270" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D270" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E270" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="I270" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J270" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A271" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B271" s="1" t="s">
+        <v>1228</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="I271" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J271" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A272" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>1232</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="I272" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J272" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>1238</v>
+      </c>
+      <c r="J273" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>1240</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D274" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E274" s="1" t="s">
+        <v>1242</v>
+      </c>
+      <c r="J274" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A275" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B275" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D275" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="E275" s="1" t="s">
+        <v>1246</v>
+      </c>
+      <c r="J275" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A276" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B276" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D276" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E276" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="J276" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A277" s="1" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B277" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D277" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="E277" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="J277" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A278" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B278" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D278" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="E278" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="J278" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A279" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B279" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D279" s="1" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E279" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="I279" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J279" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A280" s="1" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B280" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="E280" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="I280" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J280" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A281" s="1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B281" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D281" s="1" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E281" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="I281" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J281" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A282" s="1" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B282" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D282" s="1" t="s">
+        <v>1273</v>
+      </c>
+      <c r="E282" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I282" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J282" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A283" s="1" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B283" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E283" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="I283" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J283" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A284" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B284" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="D284" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E284" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="I284" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J284" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A285" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B285" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D285" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="H285" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="I285" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J285" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A286" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B286" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D286" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="H286" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="I286" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J286" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A287" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B287" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D287" s="1" t="s">
+        <v>1300</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>1302</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="H287" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="I287" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J287" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A288" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B288" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D288" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="H288" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I288" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J288" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A289" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B289" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="H289" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="I289" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J289" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="H290" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="I290" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J290" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D291" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="H291" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="I291" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J291" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A292" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D292" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="H292" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="I292" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J292" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="H293" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="I293" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J293" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D294" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H294" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I294" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J294" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A295" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B295" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H295" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="I295" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J295" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A296" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B296" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>1365</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="H296" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="I296" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J296" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A297" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B297" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D297" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="H297" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="I297" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J297" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="298" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A298" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B298" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="D298" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="H298" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="I298" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="J298" s="1" t="s">
+        <v>1037</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\fb\resources\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F91F49F-E44A-4417-9175-3396BC99589A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4942B40-ECB8-44FB-8B4C-9EB5F14915A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2AD1A0EA-2C47-4BED-8190-24EDA4F164BF}"/>
   </bookViews>
   <sheets>
     <sheet name="spell" sheetId="1" r:id="rId1"/>
@@ -3127,12 +3127,6 @@
     <t>14</t>
   </si>
   <si>
-    <t>의태시약</t>
-  </si>
-  <si>
-    <t>scripts/spell/의태시약.lua</t>
-  </si>
-  <si>
     <t>ON_CAST_14</t>
   </si>
   <si>
@@ -3149,12 +3143,6 @@
   </si>
   <si>
     <t>15</t>
-  </si>
-  <si>
-    <t>의태시약10</t>
-  </si>
-  <si>
-    <t>scripts/spell/의태시약10.lua</t>
   </si>
   <si>
     <t>ON_CAST_15</t>
@@ -4512,6 +4500,22 @@
   </si>
   <si>
     <t>scripts/spell/용천제구격.lua</t>
+  </si>
+  <si>
+    <t>의태</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/spell/정지.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>scripts/spell/의태.lua</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9799,2220 +9803,2220 @@
         <v>1030</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>1031</v>
+        <v>1489</v>
       </c>
       <c r="C219" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D219" s="1" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E219" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F219" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="E219" s="1" t="s">
+      <c r="G219" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="F219" s="1" t="s">
+      <c r="I219" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="G219" s="1" t="s">
+      <c r="J219" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="I219" s="1" t="s">
-        <v>1036</v>
-      </c>
-      <c r="J219" s="1" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>1039</v>
+        <v>1490</v>
       </c>
       <c r="C220" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>1040</v>
+        <v>1491</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="G220" s="1" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="I220" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J220" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="C221" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="G221" s="1" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="I221" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J221" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C222" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="I222" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J222" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>1382</v>
+        <v>1378</v>
       </c>
       <c r="C223" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>1475</v>
+        <v>1471</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="G223" s="1" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="I223" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J223" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>1383</v>
+        <v>1379</v>
       </c>
       <c r="C224" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>1476</v>
+        <v>1472</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F224" s="1" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="G224" s="1" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="I224" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J224" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>1384</v>
+        <v>1380</v>
       </c>
       <c r="C225" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>1477</v>
+        <v>1473</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="I225" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J225" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>1385</v>
+        <v>1381</v>
       </c>
       <c r="C226" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>1478</v>
+        <v>1474</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="G226" s="1" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="I226" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J226" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>1386</v>
+        <v>1382</v>
       </c>
       <c r="C227" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>1479</v>
+        <v>1475</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="F227" s="1" t="s">
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="G227" s="1" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="I227" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J227" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>1387</v>
+        <v>1383</v>
       </c>
       <c r="C228" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>1480</v>
+        <v>1476</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>1090</v>
+        <v>1086</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>1091</v>
+        <v>1087</v>
       </c>
       <c r="I228" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J228" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1" t="s">
-        <v>1092</v>
+        <v>1088</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>1388</v>
+        <v>1384</v>
       </c>
       <c r="C229" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>1481</v>
+        <v>1477</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="G229" s="1" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="I229" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J229" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>1389</v>
+        <v>1385</v>
       </c>
       <c r="C230" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>1482</v>
+        <v>1478</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="F230" s="1" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="G230" s="1" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="I230" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J230" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>1390</v>
+        <v>1386</v>
       </c>
       <c r="C231" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>1483</v>
+        <v>1479</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="F231" s="1" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="G231" s="1" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="I231" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J231" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1" t="s">
-        <v>1400</v>
+        <v>1396</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>1391</v>
+        <v>1387</v>
       </c>
       <c r="C232" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>1457</v>
+        <v>1453</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>1438</v>
+        <v>1434</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>1420</v>
+        <v>1416</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J232" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>1392</v>
+        <v>1388</v>
       </c>
       <c r="C233" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>1113</v>
+        <v>1109</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="G233" s="1" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="I233" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J233" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>1393</v>
+        <v>1389</v>
       </c>
       <c r="C234" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="F234" s="1" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="G234" s="1" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="I234" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J234" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="C235" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="G235" s="1" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="I235" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J235" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1" t="s">
-        <v>1128</v>
+        <v>1124</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>1395</v>
+        <v>1391</v>
       </c>
       <c r="C236" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>1488</v>
+        <v>1484</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>1131</v>
+        <v>1127</v>
       </c>
       <c r="F236" s="1" t="s">
-        <v>1132</v>
+        <v>1128</v>
       </c>
       <c r="G236" s="1" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="I236" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J236" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1" t="s">
-        <v>1134</v>
+        <v>1130</v>
       </c>
       <c r="B237" s="1" t="s">
-        <v>1396</v>
+        <v>1392</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>1489</v>
+        <v>1485</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="F237" s="1" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="I237" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J237" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="B238" s="1" t="s">
-        <v>1397</v>
+        <v>1393</v>
       </c>
       <c r="C238" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>1490</v>
+        <v>1486</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>1143</v>
+        <v>1139</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>1144</v>
+        <v>1140</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>1145</v>
+        <v>1141</v>
       </c>
       <c r="I238" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J238" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1" t="s">
-        <v>1146</v>
+        <v>1142</v>
       </c>
       <c r="B239" s="1" t="s">
-        <v>1398</v>
+        <v>1394</v>
       </c>
       <c r="C239" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>1491</v>
+        <v>1487</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="G239" s="1" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="I239" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J239" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>1399</v>
+        <v>1395</v>
       </c>
       <c r="C240" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>1492</v>
+        <v>1488</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="F240" s="1" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="I240" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J240" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="C241" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="G241" s="1" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="I241" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J241" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1" t="s">
-        <v>1401</v>
+        <v>1397</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="C242" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>1458</v>
+        <v>1454</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>1439</v>
+        <v>1435</v>
       </c>
       <c r="G242" s="1" t="s">
-        <v>1421</v>
+        <v>1417</v>
       </c>
       <c r="I242" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J242" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1" t="s">
-        <v>1402</v>
+        <v>1398</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="C243" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>1459</v>
+        <v>1455</v>
       </c>
       <c r="F243" s="1" t="s">
-        <v>1440</v>
+        <v>1436</v>
       </c>
       <c r="G243" s="1" t="s">
-        <v>1422</v>
+        <v>1418</v>
       </c>
       <c r="I243" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J243" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1" t="s">
-        <v>1403</v>
+        <v>1399</v>
       </c>
       <c r="B244" s="1" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C244" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>1460</v>
+        <v>1456</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>1441</v>
+        <v>1437</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>1423</v>
+        <v>1419</v>
       </c>
       <c r="I244" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J244" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1" t="s">
-        <v>1404</v>
+        <v>1400</v>
       </c>
       <c r="B245" s="1" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C245" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>1461</v>
+        <v>1457</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>1442</v>
+        <v>1438</v>
       </c>
       <c r="G245" s="1" t="s">
-        <v>1424</v>
+        <v>1420</v>
       </c>
       <c r="I245" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J245" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>1443</v>
+        <v>1439</v>
       </c>
       <c r="G246" s="1" t="s">
-        <v>1425</v>
+        <v>1421</v>
       </c>
       <c r="I246" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J246" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1" t="s">
-        <v>1406</v>
+        <v>1402</v>
       </c>
       <c r="B247" s="1" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="C247" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>1463</v>
+        <v>1459</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>1444</v>
+        <v>1440</v>
       </c>
       <c r="G247" s="1" t="s">
-        <v>1426</v>
+        <v>1422</v>
       </c>
       <c r="I247" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J247" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1" t="s">
-        <v>1407</v>
+        <v>1403</v>
       </c>
       <c r="B248" s="1" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="C248" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>1464</v>
+        <v>1460</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>1445</v>
+        <v>1441</v>
       </c>
       <c r="G248" s="1" t="s">
-        <v>1427</v>
+        <v>1423</v>
       </c>
       <c r="I248" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J248" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1" t="s">
-        <v>1408</v>
+        <v>1404</v>
       </c>
       <c r="B249" s="1" t="s">
-        <v>1105</v>
+        <v>1101</v>
       </c>
       <c r="C249" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>1465</v>
+        <v>1461</v>
       </c>
       <c r="F249" s="1" t="s">
-        <v>1446</v>
+        <v>1442</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>1428</v>
+        <v>1424</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J249" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1" t="s">
-        <v>1409</v>
+        <v>1405</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>1466</v>
+        <v>1462</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>1447</v>
+        <v>1443</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>1429</v>
+        <v>1425</v>
       </c>
       <c r="I250" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J250" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1" t="s">
-        <v>1410</v>
+        <v>1406</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>1467</v>
+        <v>1463</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>1448</v>
+        <v>1444</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>1430</v>
+        <v>1426</v>
       </c>
       <c r="I251" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J251" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>1124</v>
+        <v>1120</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>1167</v>
+        <v>1163</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>1169</v>
+        <v>1165</v>
       </c>
       <c r="I252" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J252" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1" t="s">
-        <v>1411</v>
+        <v>1407</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>1468</v>
+        <v>1464</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>1449</v>
+        <v>1445</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>1431</v>
+        <v>1427</v>
       </c>
       <c r="I253" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J253" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1" t="s">
-        <v>1412</v>
+        <v>1408</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>1469</v>
+        <v>1465</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>1450</v>
+        <v>1446</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>1432</v>
+        <v>1428</v>
       </c>
       <c r="I254" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J254" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1" t="s">
-        <v>1170</v>
+        <v>1166</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>1142</v>
+        <v>1138</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>1173</v>
+        <v>1169</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="I255" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J255" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1" t="s">
-        <v>1413</v>
+        <v>1409</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>1470</v>
+        <v>1466</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>1451</v>
+        <v>1447</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="I256" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J256" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1" t="s">
-        <v>1414</v>
+        <v>1410</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>1471</v>
+        <v>1467</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>1452</v>
+        <v>1448</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="I257" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J257" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1" t="s">
-        <v>1415</v>
+        <v>1411</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>1472</v>
+        <v>1468</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>1453</v>
+        <v>1449</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
       <c r="I258" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J258" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1" t="s">
-        <v>1416</v>
+        <v>1412</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>1473</v>
+        <v>1469</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>1454</v>
+        <v>1450</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="J259" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1" t="s">
-        <v>1417</v>
+        <v>1413</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>1171</v>
+        <v>1167</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>1474</v>
+        <v>1470</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1455</v>
+        <v>1451</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1437</v>
+        <v>1433</v>
       </c>
       <c r="H260" s="1" t="s">
-        <v>1456</v>
+        <v>1452</v>
       </c>
       <c r="I260" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J260" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B261" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D261" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E261" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F261" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="B261" s="1" t="s">
+      <c r="G261" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="C261" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D261" s="1" t="s">
-        <v>1178</v>
-      </c>
-      <c r="E261" s="1" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F261" s="1" t="s">
-        <v>1180</v>
-      </c>
-      <c r="G261" s="1" t="s">
-        <v>1181</v>
-      </c>
       <c r="J261" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B262" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D262" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="E262" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F262" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="B262" s="1" t="s">
+      <c r="G262" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="C262" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D262" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="E262" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F262" s="1" t="s">
-        <v>1186</v>
-      </c>
-      <c r="G262" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="J262" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1" t="s">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="I263" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J263" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B264" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D264" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="E264" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F264" s="1" t="s">
         <v>1192</v>
       </c>
-      <c r="B264" s="1" t="s">
+      <c r="G264" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="C264" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D264" s="1" t="s">
+      <c r="H264" s="1" t="s">
         <v>1194</v>
       </c>
-      <c r="E264" s="1" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F264" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G264" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="H264" s="1" t="s">
-        <v>1198</v>
-      </c>
       <c r="J264" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1" t="s">
-        <v>1418</v>
+        <v>1414</v>
       </c>
       <c r="B265" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D265" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E265" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F265" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G265" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="C265" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D265" s="1" t="s">
+      <c r="H265" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="E265" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F265" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G265" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="H265" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="J265" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1" t="s">
-        <v>1419</v>
+        <v>1415</v>
       </c>
       <c r="B266" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="D266" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="E266" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F266" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="G266" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="C266" s="1" t="s">
-        <v>640</v>
-      </c>
-      <c r="D266" s="1" t="s">
+      <c r="H266" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="E266" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F266" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="G266" s="1" t="s">
-        <v>1209</v>
-      </c>
-      <c r="H266" s="1" t="s">
-        <v>1210</v>
-      </c>
       <c r="J266" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1" t="s">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1214</v>
+        <v>1210</v>
       </c>
       <c r="J267" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1" t="s">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="I268" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J268" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1221</v>
+        <v>1217</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="I269" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J269" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1" t="s">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1225</v>
+        <v>1221</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1226</v>
+        <v>1222</v>
       </c>
       <c r="I270" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J270" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1" t="s">
-        <v>1227</v>
+        <v>1223</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1228</v>
+        <v>1224</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1229</v>
+        <v>1225</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>1230</v>
+        <v>1226</v>
       </c>
       <c r="I271" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J271" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1" t="s">
-        <v>1231</v>
+        <v>1227</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1232</v>
+        <v>1228</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>1233</v>
+        <v>1229</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>1234</v>
+        <v>1230</v>
       </c>
       <c r="I272" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J272" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1" t="s">
-        <v>1235</v>
+        <v>1231</v>
       </c>
       <c r="B273" s="1" t="s">
-        <v>1236</v>
+        <v>1232</v>
       </c>
       <c r="C273" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="J273" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1" t="s">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>1240</v>
+        <v>1236</v>
       </c>
       <c r="C274" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>1241</v>
+        <v>1237</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="J274" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="B275" s="1" t="s">
-        <v>1244</v>
+        <v>1240</v>
       </c>
       <c r="C275" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>1245</v>
+        <v>1241</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>1246</v>
+        <v>1242</v>
       </c>
       <c r="J275" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="B276" s="1" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C276" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="J276" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1" t="s">
-        <v>1251</v>
+        <v>1247</v>
       </c>
       <c r="B277" s="1" t="s">
-        <v>1252</v>
+        <v>1248</v>
       </c>
       <c r="C277" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>1253</v>
+        <v>1249</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>1254</v>
+        <v>1250</v>
       </c>
       <c r="J277" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1" t="s">
-        <v>1255</v>
+        <v>1251</v>
       </c>
       <c r="B278" s="1" t="s">
-        <v>1256</v>
+        <v>1252</v>
       </c>
       <c r="C278" s="1" t="s">
         <v>640</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="J278" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1" t="s">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="B279" s="1" t="s">
-        <v>1260</v>
+        <v>1256</v>
       </c>
       <c r="C279" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>1262</v>
+        <v>1258</v>
       </c>
       <c r="I279" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J279" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1" t="s">
-        <v>1263</v>
+        <v>1259</v>
       </c>
       <c r="B280" s="1" t="s">
-        <v>1264</v>
+        <v>1260</v>
       </c>
       <c r="C280" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>1266</v>
+        <v>1262</v>
       </c>
       <c r="I280" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J280" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1" t="s">
-        <v>1267</v>
+        <v>1263</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1268</v>
+        <v>1264</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="I281" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J281" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1" t="s">
-        <v>1271</v>
+        <v>1267</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1272</v>
+        <v>1268</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1273</v>
+        <v>1269</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1274</v>
+        <v>1270</v>
       </c>
       <c r="I282" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J282" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1" t="s">
-        <v>1275</v>
+        <v>1271</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1276</v>
+        <v>1272</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1277</v>
+        <v>1273</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="I283" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J283" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1" t="s">
-        <v>1279</v>
+        <v>1275</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1280</v>
+        <v>1276</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>641</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1281</v>
+        <v>1277</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="I284" s="1" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="J284" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1" t="s">
-        <v>1283</v>
+        <v>1279</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1284</v>
+        <v>1280</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D285" s="1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="E285" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="F285" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="G285" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="H285" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="E285" s="1" t="s">
+      <c r="I285" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="F285" s="1" t="s">
-        <v>1287</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="H285" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="I285" s="1" t="s">
-        <v>1290</v>
-      </c>
       <c r="J285" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1292</v>
+        <v>1288</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D286" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E286" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F286" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="G286" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="H286" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="E286" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="F286" s="1" t="s">
-        <v>1295</v>
-      </c>
-      <c r="G286" s="1" t="s">
-        <v>1296</v>
-      </c>
-      <c r="H286" s="1" t="s">
-        <v>1297</v>
-      </c>
       <c r="I286" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J286" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1" t="s">
-        <v>1298</v>
+        <v>1294</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1299</v>
+        <v>1295</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D287" s="1" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F287" s="1" t="s">
+        <v>1298</v>
+      </c>
+      <c r="G287" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="H287" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="E287" s="1" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F287" s="1" t="s">
-        <v>1302</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>1303</v>
-      </c>
-      <c r="H287" s="1" t="s">
-        <v>1304</v>
-      </c>
       <c r="I287" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J287" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1" t="s">
-        <v>1305</v>
+        <v>1301</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1306</v>
+        <v>1302</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D288" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="E288" s="1" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F288" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G288" s="1" t="s">
+        <v>1306</v>
+      </c>
+      <c r="H288" s="1" t="s">
         <v>1307</v>
       </c>
-      <c r="E288" s="1" t="s">
-        <v>1308</v>
-      </c>
-      <c r="F288" s="1" t="s">
-        <v>1309</v>
-      </c>
-      <c r="G288" s="1" t="s">
-        <v>1310</v>
-      </c>
-      <c r="H288" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="I288" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J288" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1" t="s">
-        <v>1312</v>
+        <v>1308</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1313</v>
+        <v>1309</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D289" s="1" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>1312</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="H289" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="E289" s="1" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F289" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="G289" s="1" t="s">
-        <v>1317</v>
-      </c>
-      <c r="H289" s="1" t="s">
-        <v>1318</v>
-      </c>
       <c r="I289" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J289" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1320</v>
+        <v>1316</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D290" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E290" s="1" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F290" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G290" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="H290" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="E290" s="1" t="s">
-        <v>1322</v>
-      </c>
-      <c r="F290" s="1" t="s">
-        <v>1323</v>
-      </c>
-      <c r="G290" s="1" t="s">
-        <v>1324</v>
-      </c>
-      <c r="H290" s="1" t="s">
-        <v>1325</v>
-      </c>
       <c r="I290" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J290" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1" t="s">
-        <v>1326</v>
+        <v>1322</v>
       </c>
       <c r="B291" s="1" t="s">
-        <v>1327</v>
+        <v>1323</v>
       </c>
       <c r="C291" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D291" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="H291" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="E291" s="1" t="s">
-        <v>1329</v>
-      </c>
-      <c r="F291" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G291" s="1" t="s">
-        <v>1331</v>
-      </c>
-      <c r="H291" s="1" t="s">
-        <v>1332</v>
-      </c>
       <c r="I291" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J291" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1" t="s">
-        <v>1333</v>
+        <v>1329</v>
       </c>
       <c r="B292" s="1" t="s">
-        <v>1334</v>
+        <v>1330</v>
       </c>
       <c r="C292" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D292" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H292" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="E292" s="1" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>1337</v>
-      </c>
-      <c r="G292" s="1" t="s">
-        <v>1338</v>
-      </c>
-      <c r="H292" s="1" t="s">
-        <v>1339</v>
-      </c>
       <c r="I292" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J292" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1" t="s">
-        <v>1340</v>
+        <v>1336</v>
       </c>
       <c r="B293" s="1" t="s">
-        <v>1341</v>
+        <v>1337</v>
       </c>
       <c r="C293" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D293" s="1" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="H293" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="E293" s="1" t="s">
-        <v>1343</v>
-      </c>
-      <c r="F293" s="1" t="s">
-        <v>1344</v>
-      </c>
-      <c r="G293" s="1" t="s">
-        <v>1345</v>
-      </c>
-      <c r="H293" s="1" t="s">
-        <v>1346</v>
-      </c>
       <c r="I293" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J293" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1" t="s">
-        <v>1347</v>
+        <v>1343</v>
       </c>
       <c r="B294" s="1" t="s">
-        <v>1348</v>
+        <v>1344</v>
       </c>
       <c r="C294" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D294" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>1348</v>
+      </c>
+      <c r="H294" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="E294" s="1" t="s">
-        <v>1350</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>1351</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>1352</v>
-      </c>
-      <c r="H294" s="1" t="s">
-        <v>1353</v>
-      </c>
       <c r="I294" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J294" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1355</v>
+        <v>1351</v>
       </c>
       <c r="C295" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D295" s="1" t="s">
+        <v>1352</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="H295" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="E295" s="1" t="s">
-        <v>1357</v>
-      </c>
-      <c r="F295" s="1" t="s">
-        <v>1358</v>
-      </c>
-      <c r="G295" s="1" t="s">
-        <v>1359</v>
-      </c>
-      <c r="H295" s="1" t="s">
-        <v>1360</v>
-      </c>
       <c r="I295" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J295" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1" t="s">
-        <v>1361</v>
+        <v>1357</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1362</v>
+        <v>1358</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D296" s="1" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E296" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F296" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="G296" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H296" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="E296" s="1" t="s">
-        <v>1364</v>
-      </c>
-      <c r="F296" s="1" t="s">
-        <v>1365</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="H296" s="1" t="s">
-        <v>1367</v>
-      </c>
       <c r="I296" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J296" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1" t="s">
-        <v>1368</v>
+        <v>1364</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1369</v>
+        <v>1365</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D297" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="E297" s="1" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F297" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="G297" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="H297" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="E297" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="F297" s="1" t="s">
-        <v>1372</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>1373</v>
-      </c>
-      <c r="H297" s="1" t="s">
-        <v>1374</v>
-      </c>
       <c r="I297" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J297" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="298" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A298" s="1" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>639</v>
       </c>
       <c r="D298" s="1" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="H298" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="E298" s="1" t="s">
-        <v>1378</v>
-      </c>
-      <c r="F298" s="1" t="s">
-        <v>1379</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>1380</v>
-      </c>
-      <c r="H298" s="1" t="s">
-        <v>1381</v>
-      </c>
       <c r="I298" s="1" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
       <c r="J298" s="1" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
     </row>
   </sheetData>

--- a/resources/table/spell.xlsx
+++ b/resources/table/spell.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E298"/>
+  <dimension ref="A1:E300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="6" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -886,54 +886,49 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>1001</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>신검합일</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>무기의 이름은?</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>다리밟기</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어디를? </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>1002</t>
-        </is>
-      </c>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>검신검귀</t>
-        </is>
-      </c>
-      <c r="C18" s="1" t="inlineStr">
-        <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="D18" s="1" t="inlineStr">
-        <is>
-          <t>무기의 이름은?</t>
-        </is>
-      </c>
-      <c r="E18" s="1" t="inlineStr">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>견우직녀축복</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>O</t>
         </is>
@@ -942,12 +937,12 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>대력검신</t>
+          <t>신검합일</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -969,22 +964,22 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="B20" s="1" t="inlineStr">
         <is>
-          <t>유인</t>
+          <t>검신검귀</t>
         </is>
       </c>
       <c r="C20" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
-          <t>대상은?</t>
+          <t>무기의 이름은?</t>
         </is>
       </c>
       <c r="E20" s="1" t="inlineStr">
@@ -996,17 +991,22 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>신의축복</t>
+          <t>대력검신</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>무기의 이름은?</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1018,17 +1018,22 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>후면공격</t>
+          <t>유인</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1040,12 +1045,12 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>1007</t>
+          <t>1005</t>
         </is>
       </c>
       <c r="B23" s="1" t="inlineStr">
         <is>
-          <t>측면공격</t>
+          <t>신의축복</t>
         </is>
       </c>
       <c r="C23" s="1" t="inlineStr">
@@ -1062,12 +1067,12 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>백호령</t>
+          <t>후면공격</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1084,12 +1089,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>이중공격</t>
+          <t>측면공격</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1106,12 +1111,12 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>삼중공격</t>
+          <t>백호령</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1128,12 +1133,12 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>사중공격</t>
+          <t>이중공격</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1150,12 +1155,12 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>오중공격</t>
+          <t>삼중공격</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1172,12 +1177,12 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>진백호령</t>
+          <t>사중공격</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1194,12 +1199,12 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1012</t>
         </is>
       </c>
       <c r="B30" s="1" t="inlineStr">
         <is>
-          <t>건곤대나이</t>
+          <t>오중공격</t>
         </is>
       </c>
       <c r="C30" s="1" t="inlineStr">
@@ -1216,12 +1221,12 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>동귀어진</t>
+          <t>진백호령</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1238,12 +1243,12 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="B32" s="1" t="inlineStr">
         <is>
-          <t>백호참</t>
+          <t>건곤대나이</t>
         </is>
       </c>
       <c r="C32" s="1" t="inlineStr">
@@ -1260,12 +1265,12 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="B33" s="1" t="inlineStr">
         <is>
-          <t>어검술</t>
+          <t>동귀어진</t>
         </is>
       </c>
       <c r="C33" s="1" t="inlineStr">
@@ -1282,12 +1287,12 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>1018</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>초혼비무</t>
+          <t>백호참</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1304,12 +1309,12 @@
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>쇄혼비무</t>
+          <t>어검술</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1326,12 +1331,12 @@
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="B36" s="1" t="inlineStr">
         <is>
-          <t>포효검황</t>
+          <t>초혼비무</t>
         </is>
       </c>
       <c r="C36" s="1" t="inlineStr">
@@ -1348,12 +1353,12 @@
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="B37" s="1" t="inlineStr">
         <is>
-          <t>혈겁만파</t>
+          <t>쇄혼비무</t>
         </is>
       </c>
       <c r="C37" s="1" t="inlineStr">
@@ -1370,12 +1375,12 @@
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="B38" s="1" t="inlineStr">
         <is>
-          <t>극'백호참</t>
+          <t>포효검황</t>
         </is>
       </c>
       <c r="C38" s="1" t="inlineStr">
@@ -1392,12 +1397,12 @@
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="B39" s="1" t="inlineStr">
         <is>
-          <t>운공체식</t>
+          <t>혈겁만파</t>
         </is>
       </c>
       <c r="C39" s="1" t="inlineStr">
@@ -1414,12 +1419,12 @@
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>1022</t>
         </is>
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>누리의빛</t>
+          <t>극'백호참</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1436,22 +1441,17 @@
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="B41" s="1" t="inlineStr">
         <is>
-          <t>금수</t>
+          <t>운공체식</t>
         </is>
       </c>
       <c r="C41" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>변신할 동물은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E41" s="1" t="inlineStr">
@@ -1463,22 +1463,17 @@
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>대지의빛</t>
+          <t>누리의빛</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1490,12 +1485,12 @@
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>경수</t>
+          <t>금수</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1517,12 +1512,12 @@
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2003</t>
         </is>
       </c>
       <c r="B44" s="1" t="inlineStr">
         <is>
-          <t>바다의빛</t>
+          <t>대지의빛</t>
         </is>
       </c>
       <c r="C44" s="1" t="inlineStr">
@@ -1544,12 +1539,12 @@
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>야수</t>
+          <t>경수</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1571,22 +1566,22 @@
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2005</t>
         </is>
       </c>
       <c r="B46" s="1" t="inlineStr">
         <is>
-          <t>맹수</t>
+          <t>바다의빛</t>
         </is>
       </c>
       <c r="C46" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D46" s="1" t="inlineStr">
         <is>
-          <t>변신할 동물은?</t>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E46" s="1" t="inlineStr">
@@ -1598,17 +1593,22 @@
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2008</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>노획</t>
+          <t>야수</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>변신할 동물은?</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1620,22 +1620,22 @@
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>망각</t>
+          <t>맹수</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>대상은?</t>
+          <t>변신할 동물은?</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -1647,12 +1647,12 @@
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2008</t>
         </is>
       </c>
       <c r="B49" s="1" t="inlineStr">
         <is>
-          <t>누리의힘</t>
+          <t>노획</t>
         </is>
       </c>
       <c r="C49" s="1" t="inlineStr">
@@ -1669,29 +1669,39 @@
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>무영보법</t>
+          <t>망각</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E50" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>투명</t>
+          <t>누리의힘</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -1708,51 +1718,51 @@
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="B52" s="1" t="inlineStr">
         <is>
-          <t>분신</t>
+          <t>무영보법</t>
         </is>
       </c>
       <c r="C52" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>2014</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="B53" s="1" t="inlineStr">
         <is>
-          <t>기문방술</t>
+          <t>투명</t>
         </is>
       </c>
       <c r="C53" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E53" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>2015</t>
+          <t>2013</t>
         </is>
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>비영승보</t>
+          <t>분신</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -1769,39 +1779,34 @@
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2014</t>
         </is>
       </c>
       <c r="B55" s="1" t="inlineStr">
         <is>
-          <t>필살검무</t>
+          <t>기문방술</t>
         </is>
       </c>
       <c r="C55" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E55" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2015</t>
         </is>
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>흡성대법</t>
+          <t>비영승보</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -1813,12 +1818,12 @@
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>이기어검</t>
+          <t>필살검무</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -1835,17 +1840,17 @@
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="B58" s="1" t="inlineStr">
         <is>
-          <t>이기어검술</t>
+          <t>흡성대법</t>
         </is>
       </c>
       <c r="C58" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="E58" s="1" t="inlineStr">
@@ -1857,12 +1862,12 @@
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="B59" s="1" t="inlineStr">
         <is>
-          <t>무형검</t>
+          <t>이기어검</t>
         </is>
       </c>
       <c r="C59" s="1" t="inlineStr">
@@ -1879,12 +1884,12 @@
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>무형술</t>
+          <t>이기어검술</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -1901,12 +1906,12 @@
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="B61" s="1" t="inlineStr">
         <is>
-          <t>파천검무</t>
+          <t>무형검</t>
         </is>
       </c>
       <c r="C61" s="1" t="inlineStr">
@@ -1923,12 +1928,12 @@
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="B62" s="1" t="inlineStr">
         <is>
-          <t>분혼경천</t>
+          <t>무형술</t>
         </is>
       </c>
       <c r="C62" s="1" t="inlineStr">
@@ -1945,12 +1950,12 @@
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="B63" s="1" t="inlineStr">
         <is>
-          <t>운기</t>
+          <t>파천검무</t>
         </is>
       </c>
       <c r="C63" s="1" t="inlineStr">
@@ -1967,105 +1972,95 @@
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="B64" s="1" t="inlineStr">
         <is>
-          <t>전혈</t>
+          <t>분혼경천</t>
         </is>
       </c>
       <c r="C64" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E64" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="B65" s="1" t="inlineStr">
         <is>
-          <t>개혈체식</t>
+          <t>운기</t>
         </is>
       </c>
       <c r="C65" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E65" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B66" s="1" t="inlineStr">
         <is>
-          <t>백호검무</t>
+          <t>전혈</t>
         </is>
       </c>
       <c r="C66" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="B67" s="1" t="inlineStr">
         <is>
-          <t>대지의힘</t>
+          <t>개혈체식</t>
         </is>
       </c>
       <c r="C67" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>3002</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B68" s="1" t="inlineStr">
         <is>
-          <t>화염주</t>
+          <t>백호검무</t>
         </is>
       </c>
       <c r="C68" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E68" s="1" t="inlineStr">
@@ -2077,12 +2072,12 @@
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>자무주</t>
+          <t>대지의힘</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2104,12 +2099,12 @@
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="B70" s="1" t="inlineStr">
         <is>
-          <t>백열주</t>
+          <t>화염주</t>
         </is>
       </c>
       <c r="C70" s="1" t="inlineStr">
@@ -2131,12 +2126,12 @@
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>3005</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="B71" s="1" t="inlineStr">
         <is>
-          <t>뢰진주</t>
+          <t>자무주</t>
         </is>
       </c>
       <c r="C71" s="1" t="inlineStr">
@@ -2158,12 +2153,12 @@
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>화영열주</t>
+          <t>백열주</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2185,12 +2180,12 @@
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="B73" s="1" t="inlineStr">
         <is>
-          <t>자영무주</t>
+          <t>뢰진주</t>
         </is>
       </c>
       <c r="C73" s="1" t="inlineStr">
@@ -2212,12 +2207,12 @@
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="B74" s="1" t="inlineStr">
         <is>
-          <t>백령주</t>
+          <t>화영열주</t>
         </is>
       </c>
       <c r="C74" s="1" t="inlineStr">
@@ -2239,12 +2234,12 @@
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="B75" s="1" t="inlineStr">
         <is>
-          <t>뢰격주</t>
+          <t>자영무주</t>
         </is>
       </c>
       <c r="C75" s="1" t="inlineStr">
@@ -2266,12 +2261,12 @@
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>3010</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>화열참주</t>
+          <t>백령주</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2293,12 +2288,12 @@
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="B77" s="1" t="inlineStr">
         <is>
-          <t>자천무주</t>
+          <t>뢰격주</t>
         </is>
       </c>
       <c r="C77" s="1" t="inlineStr">
@@ -2320,12 +2315,12 @@
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>3012</t>
+          <t>3010</t>
         </is>
       </c>
       <c r="B78" s="1" t="inlineStr">
         <is>
-          <t>백열참주</t>
+          <t>화열참주</t>
         </is>
       </c>
       <c r="C78" s="1" t="inlineStr">
@@ -2347,12 +2342,12 @@
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3011</t>
         </is>
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>뢰격참주</t>
+          <t>자천무주</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2374,12 +2369,12 @@
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>3014</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="B80" s="1" t="inlineStr">
         <is>
-          <t>진화열참주</t>
+          <t>백열참주</t>
         </is>
       </c>
       <c r="C80" s="1" t="inlineStr">
@@ -2401,12 +2396,12 @@
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="B81" s="1" t="inlineStr">
         <is>
-          <t>진자천무주</t>
+          <t>뢰격참주</t>
         </is>
       </c>
       <c r="C81" s="1" t="inlineStr">
@@ -2428,12 +2423,12 @@
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="B82" s="1" t="inlineStr">
         <is>
-          <t>진백열참주</t>
+          <t>진화열참주</t>
         </is>
       </c>
       <c r="C82" s="1" t="inlineStr">
@@ -2455,12 +2450,12 @@
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>진뢰격참주</t>
+          <t>진자천무주</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -2482,12 +2477,12 @@
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="B84" s="1" t="inlineStr">
         <is>
-          <t>극진화열참주</t>
+          <t>진백열참주</t>
         </is>
       </c>
       <c r="C84" s="1" t="inlineStr">
@@ -2509,12 +2504,12 @@
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>극진자천무주</t>
+          <t>진뢰격참주</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -2536,12 +2531,12 @@
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>3020</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="B86" s="1" t="inlineStr">
         <is>
-          <t>극진백열참주</t>
+          <t>극진화열참주</t>
         </is>
       </c>
       <c r="C86" s="1" t="inlineStr">
@@ -2563,12 +2558,12 @@
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>극진뢰격참주</t>
+          <t>극진자천무주</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -2590,17 +2585,22 @@
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="B88" s="1" t="inlineStr">
         <is>
-          <t>화염주'첨</t>
+          <t>극진백열참주</t>
         </is>
       </c>
       <c r="C88" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E88" s="1" t="inlineStr">
@@ -2612,17 +2612,22 @@
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="B89" s="1" t="inlineStr">
         <is>
-          <t>자무주'첨</t>
+          <t>극진뢰격참주</t>
         </is>
       </c>
       <c r="C89" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E89" s="1" t="inlineStr">
@@ -2634,12 +2639,12 @@
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3022</t>
         </is>
       </c>
       <c r="B90" s="1" t="inlineStr">
         <is>
-          <t>백열주'첨</t>
+          <t>화염주'첨</t>
         </is>
       </c>
       <c r="C90" s="1" t="inlineStr">
@@ -2656,12 +2661,12 @@
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="B91" s="1" t="inlineStr">
         <is>
-          <t>뢰진주'첨</t>
+          <t>자무주'첨</t>
         </is>
       </c>
       <c r="C91" s="1" t="inlineStr">
@@ -2678,12 +2683,12 @@
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="B92" s="1" t="inlineStr">
         <is>
-          <t>화영열주'첨</t>
+          <t>백열주'첨</t>
         </is>
       </c>
       <c r="C92" s="1" t="inlineStr">
@@ -2700,12 +2705,12 @@
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="B93" s="1" t="inlineStr">
         <is>
-          <t>자영무주'첨</t>
+          <t>뢰진주'첨</t>
         </is>
       </c>
       <c r="C93" s="1" t="inlineStr">
@@ -2722,12 +2727,12 @@
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>백령주'첨</t>
+          <t>화영열주'첨</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -2744,12 +2749,12 @@
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="B95" s="1" t="inlineStr">
         <is>
-          <t>뢰격주'첨</t>
+          <t>자영무주'첨</t>
         </is>
       </c>
       <c r="C95" s="1" t="inlineStr">
@@ -2766,12 +2771,12 @@
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="B96" s="1" t="inlineStr">
         <is>
-          <t>화열참주'첨</t>
+          <t>백령주'첨</t>
         </is>
       </c>
       <c r="C96" s="1" t="inlineStr">
@@ -2788,12 +2793,12 @@
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>3031</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="B97" s="1" t="inlineStr">
         <is>
-          <t>자천무주'첨</t>
+          <t>뢰격주'첨</t>
         </is>
       </c>
       <c r="C97" s="1" t="inlineStr">
@@ -2810,12 +2815,12 @@
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="B98" s="1" t="inlineStr">
         <is>
-          <t>백열참주'첨</t>
+          <t>화열참주'첨</t>
         </is>
       </c>
       <c r="C98" s="1" t="inlineStr">
@@ -2832,12 +2837,12 @@
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>3033</t>
+          <t>3031</t>
         </is>
       </c>
       <c r="B99" s="1" t="inlineStr">
         <is>
-          <t>뢰격참주'첨</t>
+          <t>자천무주'첨</t>
         </is>
       </c>
       <c r="C99" s="1" t="inlineStr">
@@ -2854,12 +2859,12 @@
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="B100" s="1" t="inlineStr">
         <is>
-          <t>진화열참주'첨</t>
+          <t>백열참주'첨</t>
         </is>
       </c>
       <c r="C100" s="1" t="inlineStr">
@@ -2876,12 +2881,12 @@
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>3035</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>진자천무주'첨</t>
+          <t>뢰격참주'첨</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
@@ -2898,12 +2903,12 @@
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B102" s="1" t="inlineStr">
         <is>
-          <t>진백열참주'첨</t>
+          <t>진화열참주'첨</t>
         </is>
       </c>
       <c r="C102" s="1" t="inlineStr">
@@ -2920,12 +2925,12 @@
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3035</t>
         </is>
       </c>
       <c r="B103" s="1" t="inlineStr">
         <is>
-          <t>진뢰격참주'첨</t>
+          <t>진자천무주'첨</t>
         </is>
       </c>
       <c r="C103" s="1" t="inlineStr">
@@ -2942,12 +2947,12 @@
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="B104" s="1" t="inlineStr">
         <is>
-          <t>극진화열참주'첨</t>
+          <t>진백열참주'첨</t>
         </is>
       </c>
       <c r="C104" s="1" t="inlineStr">
@@ -2964,12 +2969,12 @@
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>3039</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>극진자천무주'첨</t>
+          <t>진뢰격참주'첨</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -2986,12 +2991,12 @@
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3038</t>
         </is>
       </c>
       <c r="B106" s="1" t="inlineStr">
         <is>
-          <t>극진백열참주'첨</t>
+          <t>극진화열참주'첨</t>
         </is>
       </c>
       <c r="C106" s="1" t="inlineStr">
@@ -3008,12 +3013,12 @@
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>극진뢰격참주'첨</t>
+          <t>극진자천무주'첨</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3030,44 +3035,39 @@
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>성려멸주</t>
+          <t>극진백열참주'첨</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E108" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="B109" s="1" t="inlineStr">
         <is>
-          <t>헬파이어</t>
+          <t>극진뢰격참주'첨</t>
         </is>
       </c>
       <c r="C109" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E109" s="1" t="inlineStr">
@@ -3079,12 +3079,12 @@
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3042</t>
         </is>
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>삼매진화</t>
+          <t>성려멸주</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3095,28 +3095,28 @@
       <c r="D110" s="1" t="inlineStr">
         <is>
           <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>3043</t>
         </is>
       </c>
       <c r="B111" s="1" t="inlineStr">
         <is>
-          <t>지폭지술</t>
+          <t>헬파이어</t>
         </is>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E111" s="1" t="inlineStr">
@@ -3128,17 +3128,22 @@
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>3046</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>폭류유성</t>
+          <t>삼매진화</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -3150,22 +3155,17 @@
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>3047</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B113" s="1" t="inlineStr">
         <is>
-          <t>현자의기원</t>
+          <t>지폭지술</t>
         </is>
       </c>
       <c r="C113" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E113" s="1" t="inlineStr">
@@ -3177,29 +3177,34 @@
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>3048</t>
+          <t>3046</t>
         </is>
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>환기</t>
+          <t>폭류유성</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E114" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>3049</t>
+          <t>3047</t>
         </is>
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>노도성황</t>
+          <t>현자의기원</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -3210,35 +3215,40 @@
       <c r="D115" s="1" t="inlineStr">
         <is>
           <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E115" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3048</t>
         </is>
       </c>
       <c r="B116" s="1" t="inlineStr">
         <is>
-          <t>몬스터노도성황</t>
+          <t>환기</t>
         </is>
       </c>
       <c r="C116" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>3051</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>저주</t>
+          <t>노도성황</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -3249,50 +3259,35 @@
       <c r="D117" s="1" t="inlineStr">
         <is>
           <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="B118" s="1" t="inlineStr">
         <is>
-          <t>마비</t>
+          <t>몬스터노도성황</t>
         </is>
       </c>
       <c r="C118" s="1" t="inlineStr">
         <is>
           <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="B119" s="1" t="inlineStr">
         <is>
-          <t>절망</t>
+          <t>저주</t>
         </is>
       </c>
       <c r="C119" s="1" t="inlineStr">
@@ -3314,12 +3309,12 @@
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>3054</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="B120" s="1" t="inlineStr">
         <is>
-          <t>혼돈</t>
+          <t>마비</t>
         </is>
       </c>
       <c r="C120" s="1" t="inlineStr">
@@ -3330,52 +3325,72 @@
       <c r="D120" s="1" t="inlineStr">
         <is>
           <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E120" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="B121" s="1" t="inlineStr">
         <is>
-          <t>호체주술</t>
+          <t>절망</t>
         </is>
       </c>
       <c r="C121" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E121" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3054</t>
         </is>
       </c>
       <c r="B122" s="1" t="inlineStr">
         <is>
-          <t>마기지체</t>
+          <t>혼돈</t>
         </is>
       </c>
       <c r="C122" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>마기지체저주</t>
+          <t>호체주술</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -3387,12 +3402,12 @@
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="B124" s="1" t="inlineStr">
         <is>
-          <t>만파지독</t>
+          <t>마기지체</t>
         </is>
       </c>
       <c r="C124" s="1" t="inlineStr">
@@ -3404,39 +3419,29 @@
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>3059</t>
+          <t>3057</t>
         </is>
       </c>
       <c r="B125" s="1" t="inlineStr">
         <is>
-          <t>중독</t>
+          <t>마기지체저주</t>
         </is>
       </c>
       <c r="C125" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3058</t>
         </is>
       </c>
       <c r="B126" s="1" t="inlineStr">
         <is>
-          <t>몬스터중독</t>
+          <t>만파지독</t>
         </is>
       </c>
       <c r="C126" s="1" t="inlineStr">
@@ -3448,22 +3453,22 @@
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3059</t>
         </is>
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>소혼강신</t>
+          <t>중독</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>소환할 동물은?</t>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -3475,44 +3480,39 @@
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>4002</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="B128" s="1" t="inlineStr">
         <is>
-          <t>공력증강</t>
+          <t>몬스터중독</t>
         </is>
       </c>
       <c r="C128" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>4003</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="B129" s="1" t="inlineStr">
         <is>
-          <t>무장</t>
+          <t>소혼강신</t>
         </is>
       </c>
       <c r="C129" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
-          <t>대상은?</t>
+          <t>소환할 동물은?</t>
         </is>
       </c>
       <c r="E129" s="1" t="inlineStr">
@@ -3524,22 +3524,17 @@
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>4004</t>
+          <t>4002</t>
         </is>
       </c>
       <c r="B130" s="1" t="inlineStr">
         <is>
-          <t>보호</t>
+          <t>공력증강</t>
         </is>
       </c>
       <c r="C130" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E130" s="1" t="inlineStr">
@@ -3551,17 +3546,22 @@
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4003</t>
         </is>
       </c>
       <c r="B131" s="1" t="inlineStr">
         <is>
-          <t>차폐</t>
+          <t>무장</t>
         </is>
       </c>
       <c r="C131" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E131" s="1" t="inlineStr">
@@ -3573,12 +3573,12 @@
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4004</t>
         </is>
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>시력회복</t>
+          <t>보호</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -3600,22 +3600,17 @@
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>4007</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>파혼술</t>
+          <t>차폐</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -3627,17 +3622,22 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>4006</t>
         </is>
       </c>
       <c r="B134" s="1" t="inlineStr">
         <is>
-          <t>심안투영</t>
+          <t>시력회복</t>
         </is>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E134" s="1" t="inlineStr">
@@ -3649,12 +3649,12 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>4009</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>혼마술</t>
+          <t>파혼술</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -3676,22 +3676,17 @@
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4008</t>
         </is>
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>공력주입</t>
+          <t>심안투영</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D136" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -3703,17 +3698,22 @@
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4009</t>
         </is>
       </c>
       <c r="B137" s="1" t="inlineStr">
         <is>
-          <t>금강불체</t>
+          <t>혼마술</t>
         </is>
       </c>
       <c r="C137" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E137" s="1" t="inlineStr">
@@ -3725,12 +3725,12 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="B138" s="1" t="inlineStr">
         <is>
-          <t>무력화</t>
+          <t>공력주입</t>
         </is>
       </c>
       <c r="C138" s="1" t="inlineStr">
@@ -3752,29 +3752,34 @@
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>4013</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="B139" s="1" t="inlineStr">
         <is>
-          <t>환마술</t>
+          <t>금강불체</t>
         </is>
       </c>
       <c r="C139" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E139" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>4012</t>
         </is>
       </c>
       <c r="B140" s="1" t="inlineStr">
         <is>
-          <t>부활</t>
+          <t>무력화</t>
         </is>
       </c>
       <c r="C140" s="1" t="inlineStr">
@@ -3796,39 +3801,39 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="B141" s="1" t="inlineStr">
         <is>
-          <t>반탄공</t>
+          <t>환마술</t>
         </is>
       </c>
       <c r="C141" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E141" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>4016</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="B142" s="1" t="inlineStr">
         <is>
-          <t>신령지익</t>
+          <t>부활</t>
         </is>
       </c>
       <c r="C142" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E142" s="1" t="inlineStr">
@@ -3840,12 +3845,12 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>신령지익진</t>
+          <t>반탄공</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -3862,12 +3867,12 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>4018</t>
+          <t>4016</t>
         </is>
       </c>
       <c r="B144" s="1" t="inlineStr">
         <is>
-          <t>파력무참</t>
+          <t>신령지익</t>
         </is>
       </c>
       <c r="C144" s="1" t="inlineStr">
@@ -3884,12 +3889,12 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>4019</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>파력무참진</t>
+          <t>신령지익진</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -3906,29 +3911,34 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4018</t>
         </is>
       </c>
       <c r="B146" s="1" t="inlineStr">
         <is>
-          <t>환군마술</t>
+          <t>파력무참</t>
         </is>
       </c>
       <c r="C146" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="E146" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="B147" s="1" t="inlineStr">
         <is>
-          <t>귀염추혼소</t>
+          <t>파력무참진</t>
         </is>
       </c>
       <c r="C147" s="1" t="inlineStr">
@@ -3945,49 +3955,34 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>4022</t>
+          <t>4020</t>
         </is>
       </c>
       <c r="B148" s="1" t="inlineStr">
         <is>
-          <t>퇴마주</t>
+          <t>환군마술</t>
         </is>
       </c>
       <c r="C148" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D148" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
-        </is>
-      </c>
-      <c r="E148" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>4021</t>
         </is>
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>해독</t>
+          <t>귀염추혼소</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D149" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -3999,12 +3994,12 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>4024</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>활력</t>
+          <t>퇴마주</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -4026,17 +4021,22 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>4025</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="B151" s="1" t="inlineStr">
         <is>
-          <t>누리의기원</t>
+          <t>해독</t>
         </is>
       </c>
       <c r="C151" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E151" s="1" t="inlineStr">
@@ -4048,17 +4048,22 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>4024</t>
         </is>
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>바다의기원</t>
+          <t>활력</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
@@ -4070,22 +4075,17 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>4025</t>
         </is>
       </c>
       <c r="B153" s="1" t="inlineStr">
         <is>
-          <t>대지의기원</t>
+          <t>누리의기원</t>
         </is>
       </c>
       <c r="C153" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D153" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E153" s="1" t="inlineStr">
@@ -4097,22 +4097,17 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>4028</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="B154" s="1" t="inlineStr">
         <is>
-          <t>동해의기원</t>
+          <t>바다의기원</t>
         </is>
       </c>
       <c r="C154" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D154" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E154" s="1" t="inlineStr">
@@ -4124,17 +4119,22 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>4029</t>
+          <t>4027</t>
         </is>
       </c>
       <c r="B155" s="1" t="inlineStr">
         <is>
-          <t>하늘의기원</t>
+          <t>대지의기원</t>
         </is>
       </c>
       <c r="C155" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E155" s="1" t="inlineStr">
@@ -4146,12 +4146,12 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="B156" s="1" t="inlineStr">
         <is>
-          <t>천공의기원</t>
+          <t>동해의기원</t>
         </is>
       </c>
       <c r="C156" s="1" t="inlineStr">
@@ -4173,22 +4173,17 @@
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
         <is>
-          <t>4031</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>천공의희원</t>
+          <t>하늘의기원</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D157" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
@@ -4200,12 +4195,12 @@
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
         <is>
-          <t>4032</t>
+          <t>4030</t>
         </is>
       </c>
       <c r="B158" s="1" t="inlineStr">
         <is>
-          <t>구름의기원</t>
+          <t>천공의기원</t>
         </is>
       </c>
       <c r="C158" s="1" t="inlineStr">
@@ -4227,12 +4222,12 @@
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
         <is>
-          <t>4033</t>
+          <t>4031</t>
         </is>
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>구름의희원</t>
+          <t>천공의희원</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -4254,12 +4249,12 @@
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
         <is>
-          <t>4034</t>
+          <t>4032</t>
         </is>
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>태양의기원</t>
+          <t>구름의기원</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
@@ -4281,12 +4276,12 @@
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
         <is>
-          <t>4035</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="B161" s="1" t="inlineStr">
         <is>
-          <t>태양의희원</t>
+          <t>구름의희원</t>
         </is>
       </c>
       <c r="C161" s="1" t="inlineStr">
@@ -4308,12 +4303,12 @@
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
         <is>
-          <t>4036</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>생명의기원</t>
+          <t>태양의기원</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -4335,12 +4330,12 @@
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="B163" s="1" t="inlineStr">
         <is>
-          <t>백호의희원</t>
+          <t>태양의희원</t>
         </is>
       </c>
       <c r="C163" s="1" t="inlineStr">
@@ -4362,12 +4357,12 @@
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4036</t>
         </is>
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>신령의기원</t>
+          <t>생명의기원</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -4389,17 +4384,22 @@
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="B165" s="1" t="inlineStr">
         <is>
-          <t>신령의기원'첨</t>
+          <t>백호의희원</t>
         </is>
       </c>
       <c r="C165" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E165" s="1" t="inlineStr">
@@ -4411,17 +4411,22 @@
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>백호의희원'첨</t>
+          <t>신령의기원</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -4433,22 +4438,17 @@
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
         <is>
-          <t>4041</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="B167" s="1" t="inlineStr">
         <is>
-          <t>봉황의기원</t>
+          <t>신령의기원'첨</t>
         </is>
       </c>
       <c r="C167" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D167" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E167" s="1" t="inlineStr">
@@ -4460,22 +4460,17 @@
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
         <is>
-          <t>4042</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="B168" s="1" t="inlineStr">
         <is>
-          <t>지진</t>
+          <t>백호의희원'첨</t>
         </is>
       </c>
       <c r="C168" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D168" s="1" t="inlineStr">
-        <is>
-          <t>대상은?</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E168" s="1" t="inlineStr">
@@ -4487,73 +4482,88 @@
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>신의소환</t>
+          <t>봉황의기원</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>소환할 대상은?</t>
+          <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E169" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>4042</t>
         </is>
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>신의출두</t>
+          <t>지진</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>출두할 대상은?</t>
+          <t>대상은?</t>
+        </is>
+      </c>
+      <c r="E170" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>잠복근무</t>
+          <t>신의소환</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>소환할 대상은?</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="B172" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">생성　</t>
+          <t>신의출두</t>
         </is>
       </c>
       <c r="C172" s="1" t="inlineStr">
@@ -4563,46 +4573,36 @@
       </c>
       <c r="D172" s="1" t="inlineStr">
         <is>
-          <t>생성할 아이템은?</t>
+          <t>출두할 대상은?</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>맵번호</t>
+          <t>잠복근무</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
-        </is>
-      </c>
-      <c r="D173" s="1" t="inlineStr">
-        <is>
-          <t>검색할 맵 이름은?</t>
-        </is>
-      </c>
-      <c r="E173" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
         <is>
-          <t>5006</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="B174" s="1" t="inlineStr">
         <is>
-          <t>세계후</t>
+          <t xml:space="preserve">생성　</t>
         </is>
       </c>
       <c r="C174" s="1" t="inlineStr">
@@ -4612,80 +4612,95 @@
       </c>
       <c r="D174" s="1" t="inlineStr">
         <is>
-          <t>할 말은?</t>
-        </is>
-      </c>
-      <c r="E174" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>생성할 아이템은?</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
         <is>
-          <t>5007</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="B175" s="1" t="inlineStr">
         <is>
-          <t>감시</t>
+          <t>맵번호</t>
         </is>
       </c>
       <c r="C175" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>INPUT</t>
         </is>
       </c>
       <c r="D175" s="1" t="inlineStr">
         <is>
-          <t>대상은?</t>
+          <t>검색할 맵 이름은?</t>
+        </is>
+      </c>
+      <c r="E175" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="B176" s="1" t="inlineStr">
         <is>
-          <t>강제이동</t>
+          <t>세계후</t>
         </is>
       </c>
       <c r="C176" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>할 말은?</t>
+        </is>
+      </c>
+      <c r="E176" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
         <is>
-          <t>5009</t>
+          <t>5007</t>
         </is>
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>압록지정</t>
+          <t>감시</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
         <is>
-          <t>UNKNOWN3</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>대상은?</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
         <is>
-          <t>6001</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>왕의저주</t>
+          <t>강제이동</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -4697,29 +4712,29 @@
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>금고주인의저주</t>
+          <t>압록지정</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>UNKNOWN3</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6001</t>
         </is>
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>귀신퇴치부적</t>
+          <t>왕의저주</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -4731,12 +4746,12 @@
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6002</t>
         </is>
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>표신궁고문서6찾기</t>
+          <t>금고주인의저주</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -4748,12 +4763,12 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>6003</t>
         </is>
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>동충하초인삼</t>
+          <t>귀신퇴치부적</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -4765,12 +4780,12 @@
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>6004</t>
         </is>
       </c>
       <c r="B183" s="1" t="inlineStr">
         <is>
-          <t>만리향씨앗</t>
+          <t>표신궁고문서6찾기</t>
         </is>
       </c>
       <c r="C183" s="1" t="inlineStr">
@@ -4782,12 +4797,12 @@
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
         <is>
-          <t>6007</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="B184" s="1" t="inlineStr">
         <is>
-          <t>변신시약</t>
+          <t>동충하초인삼</t>
         </is>
       </c>
       <c r="C184" s="1" t="inlineStr">
@@ -4799,12 +4814,12 @@
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
         <is>
-          <t>6008</t>
+          <t>6006</t>
         </is>
       </c>
       <c r="B185" s="1" t="inlineStr">
         <is>
-          <t>만리장성수리</t>
+          <t>만리향씨앗</t>
         </is>
       </c>
       <c r="C185" s="1" t="inlineStr">
@@ -4816,12 +4831,12 @@
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6007</t>
         </is>
       </c>
       <c r="B186" s="1" t="inlineStr">
         <is>
-          <t>적심토</t>
+          <t>변신시약</t>
         </is>
       </c>
       <c r="C186" s="1" t="inlineStr">
@@ -4833,12 +4848,12 @@
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>6008</t>
         </is>
       </c>
       <c r="B187" s="1" t="inlineStr">
         <is>
-          <t>멍석말이</t>
+          <t>만리장성수리</t>
         </is>
       </c>
       <c r="C187" s="1" t="inlineStr">
@@ -4850,12 +4865,12 @@
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6009</t>
         </is>
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>승급보상</t>
+          <t>적심토</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -4867,12 +4882,12 @@
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="B189" s="1" t="inlineStr">
         <is>
-          <t>결혼체크</t>
+          <t>멍석말이</t>
         </is>
       </c>
       <c r="C189" s="1" t="inlineStr">
@@ -4884,12 +4899,12 @@
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>옥좌점령</t>
+          <t>승급보상</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -4901,12 +4916,12 @@
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="B191" s="1" t="inlineStr">
         <is>
-          <t>거륵주독</t>
+          <t>결혼체크</t>
         </is>
       </c>
       <c r="C191" s="1" t="inlineStr">
@@ -4918,12 +4933,12 @@
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
         <is>
-          <t>6015</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="B192" s="1" t="inlineStr">
         <is>
-          <t>록란조</t>
+          <t>옥좌점령</t>
         </is>
       </c>
       <c r="C192" s="1" t="inlineStr">
@@ -4935,12 +4950,12 @@
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
         <is>
-          <t>6016</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>태자의장난감</t>
+          <t>거륵주독</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -4952,12 +4967,12 @@
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="B194" s="1" t="inlineStr">
         <is>
-          <t>주작의검</t>
+          <t>록란조</t>
         </is>
       </c>
       <c r="C194" s="1" t="inlineStr">
@@ -4969,12 +4984,12 @@
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>현무의검</t>
+          <t>태자의장난감</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -4986,12 +5001,12 @@
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
         <is>
-          <t>6019</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="B196" s="1" t="inlineStr">
         <is>
-          <t>청룡의검</t>
+          <t>주작의검</t>
         </is>
       </c>
       <c r="C196" s="1" t="inlineStr">
@@ -5003,12 +5018,12 @@
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>6018</t>
         </is>
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>백호의검</t>
+          <t>현무의검</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -5020,12 +5035,12 @@
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="B198" s="1" t="inlineStr">
         <is>
-          <t>산신의보물지도</t>
+          <t>청룡의검</t>
         </is>
       </c>
       <c r="C198" s="1" t="inlineStr">
@@ -5037,12 +5052,12 @@
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>여신의이슬</t>
+          <t>백호의검</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -5054,12 +5069,12 @@
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="B200" s="1" t="inlineStr">
         <is>
-          <t>청심초</t>
+          <t>산신의보물지도</t>
         </is>
       </c>
       <c r="C200" s="1" t="inlineStr">
@@ -5071,12 +5086,12 @@
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="B201" s="1" t="inlineStr">
         <is>
-          <t>복홍잡기</t>
+          <t>여신의이슬</t>
         </is>
       </c>
       <c r="C201" s="1" t="inlineStr">
@@ -5088,12 +5103,12 @@
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
         <is>
-          <t>7002</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="B202" s="1" t="inlineStr">
         <is>
-          <t>태자전음문서</t>
+          <t>청심초</t>
         </is>
       </c>
       <c r="C202" s="1" t="inlineStr">
@@ -5105,12 +5120,12 @@
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>게장군포박</t>
+          <t>복홍잡기</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -5122,12 +5137,12 @@
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
         <is>
-          <t>7004</t>
+          <t>7002</t>
         </is>
       </c>
       <c r="B204" s="1" t="inlineStr">
         <is>
-          <t>문어장군포박</t>
+          <t>태자전음문서</t>
         </is>
       </c>
       <c r="C204" s="1" t="inlineStr">
@@ -5139,12 +5154,12 @@
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
         <is>
-          <t>7005</t>
+          <t>7003</t>
         </is>
       </c>
       <c r="B205" s="1" t="inlineStr">
         <is>
-          <t>해마병사잡기</t>
+          <t>게장군포박</t>
         </is>
       </c>
       <c r="C205" s="1" t="inlineStr">
@@ -5156,12 +5171,12 @@
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>7004</t>
         </is>
       </c>
       <c r="B206" s="1" t="inlineStr">
         <is>
-          <t>해마장군잡기</t>
+          <t>문어장군포박</t>
         </is>
       </c>
       <c r="C206" s="1" t="inlineStr">
@@ -5173,12 +5188,12 @@
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>7005</t>
         </is>
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>인어장군잡기</t>
+          <t>해마병사잡기</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -5190,12 +5205,12 @@
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>상어장군잡기</t>
+          <t>해마장군잡기</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -5207,12 +5222,12 @@
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="B209" s="1" t="inlineStr">
         <is>
-          <t>해파리장군잡기</t>
+          <t>인어장군잡기</t>
         </is>
       </c>
       <c r="C209" s="1" t="inlineStr">
@@ -5224,12 +5239,12 @@
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>7008</t>
         </is>
       </c>
       <c r="B210" s="1" t="inlineStr">
         <is>
-          <t>전략문서</t>
+          <t>상어장군잡기</t>
         </is>
       </c>
       <c r="C210" s="1" t="inlineStr">
@@ -5241,12 +5256,12 @@
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
         <is>
-          <t>7011</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>청의태자포획</t>
+          <t>해파리장군잡기</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -5258,12 +5273,12 @@
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="B212" s="1" t="inlineStr">
         <is>
-          <t>토깽이포획</t>
+          <t>전략문서</t>
         </is>
       </c>
       <c r="C212" s="1" t="inlineStr">
@@ -5275,61 +5290,51 @@
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="B213" s="1" t="inlineStr">
         <is>
-          <t>청룡마령참</t>
+          <t>청의태자포획</t>
         </is>
       </c>
       <c r="C213" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="E213" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
+          <t>NORMAL</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="B214" s="1" t="inlineStr">
         <is>
-          <t>강제이동(상)</t>
+          <t>토깽이포획</t>
         </is>
       </c>
       <c r="C214" s="1" t="inlineStr">
         <is>
           <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="E214" s="1" t="inlineStr">
-        <is>
-          <t>O</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
         <is>
-          <t>10001</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>강제이동(하)</t>
+          <t>청룡마령참</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -5341,12 +5346,12 @@
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10000</t>
         </is>
       </c>
       <c r="B216" s="1" t="inlineStr">
         <is>
-          <t>강제이동(좌)</t>
+          <t>강제이동(상)</t>
         </is>
       </c>
       <c r="C216" s="1" t="inlineStr">
@@ -5363,12 +5368,12 @@
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
         <is>
-          <t>10003</t>
+          <t>10001</t>
         </is>
       </c>
       <c r="B217" s="1" t="inlineStr">
         <is>
-          <t>강제이동(우)</t>
+          <t>강제이동(하)</t>
         </is>
       </c>
       <c r="C217" s="1" t="inlineStr">
@@ -5385,17 +5390,17 @@
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10002</t>
         </is>
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>월아일격</t>
+          <t>강제이동(좌)</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -5407,22 +5412,17 @@
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>10003</t>
         </is>
       </c>
       <c r="B219" s="1" t="inlineStr">
         <is>
-          <t>의태</t>
+          <t>강제이동(우)</t>
         </is>
       </c>
       <c r="C219" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D219" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E219" s="1" t="inlineStr">
@@ -5434,22 +5434,17 @@
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10004</t>
         </is>
       </c>
       <c r="B220" s="1" t="inlineStr">
         <is>
-          <t>정지</t>
+          <t>월아일격</t>
         </is>
       </c>
       <c r="C220" s="1" t="inlineStr">
         <is>
           <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D220" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E220" s="1" t="inlineStr">
@@ -5461,12 +5456,12 @@
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B221" s="1" t="inlineStr">
         <is>
-          <t>시약보호</t>
+          <t>의태</t>
         </is>
       </c>
       <c r="C221" s="1" t="inlineStr">
@@ -5488,12 +5483,12 @@
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B222" s="1" t="inlineStr">
         <is>
-          <t>시약무장</t>
+          <t>정지</t>
         </is>
       </c>
       <c r="C222" s="1" t="inlineStr">
@@ -5515,12 +5510,12 @@
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>용마제일격</t>
+          <t>시약보호</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
@@ -5542,12 +5537,12 @@
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B224" s="1" t="inlineStr">
         <is>
-          <t>용마제이격</t>
+          <t>시약무장</t>
         </is>
       </c>
       <c r="C224" s="1" t="inlineStr">
@@ -5569,12 +5564,12 @@
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B225" s="1" t="inlineStr">
         <is>
-          <t>용마제삼격</t>
+          <t>용마제일격</t>
         </is>
       </c>
       <c r="C225" s="1" t="inlineStr">
@@ -5596,12 +5591,12 @@
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B226" s="1" t="inlineStr">
         <is>
-          <t>용마제사격</t>
+          <t>용마제이격</t>
         </is>
       </c>
       <c r="C226" s="1" t="inlineStr">
@@ -5623,12 +5618,12 @@
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B227" s="1" t="inlineStr">
         <is>
-          <t>용마제오격</t>
+          <t>용마제삼격</t>
         </is>
       </c>
       <c r="C227" s="1" t="inlineStr">
@@ -5650,12 +5645,12 @@
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B228" s="1" t="inlineStr">
         <is>
-          <t>용마제육격</t>
+          <t>용마제사격</t>
         </is>
       </c>
       <c r="C228" s="1" t="inlineStr">
@@ -5677,12 +5672,12 @@
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B229" s="1" t="inlineStr">
         <is>
-          <t>용마제칠격</t>
+          <t>용마제오격</t>
         </is>
       </c>
       <c r="C229" s="1" t="inlineStr">
@@ -5704,12 +5699,12 @@
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B230" s="1" t="inlineStr">
         <is>
-          <t>용마제팔격</t>
+          <t>용마제육격</t>
         </is>
       </c>
       <c r="C230" s="1" t="inlineStr">
@@ -5731,12 +5726,12 @@
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B231" s="1" t="inlineStr">
         <is>
-          <t>용마제구격</t>
+          <t>용마제칠격</t>
         </is>
       </c>
       <c r="C231" s="1" t="inlineStr">
@@ -5758,12 +5753,12 @@
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B232" s="1" t="inlineStr">
         <is>
-          <t>용천제일격</t>
+          <t>용마제팔격</t>
         </is>
       </c>
       <c r="C232" s="1" t="inlineStr">
@@ -5785,12 +5780,12 @@
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B233" s="1" t="inlineStr">
         <is>
-          <t>용천제이격</t>
+          <t>용마제구격</t>
         </is>
       </c>
       <c r="C233" s="1" t="inlineStr">
@@ -5812,12 +5807,12 @@
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B234" s="1" t="inlineStr">
         <is>
-          <t>용천제삼격</t>
+          <t>용천제일격</t>
         </is>
       </c>
       <c r="C234" s="1" t="inlineStr">
@@ -5839,12 +5834,12 @@
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B235" s="1" t="inlineStr">
         <is>
-          <t>용천제사격</t>
+          <t>용천제이격</t>
         </is>
       </c>
       <c r="C235" s="1" t="inlineStr">
@@ -5866,12 +5861,12 @@
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B236" s="1" t="inlineStr">
         <is>
-          <t>용천제오격</t>
+          <t>용천제삼격</t>
         </is>
       </c>
       <c r="C236" s="1" t="inlineStr">
@@ -5893,12 +5888,12 @@
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B237" s="1" t="inlineStr">
         <is>
-          <t>용천제육격</t>
+          <t>용천제사격</t>
         </is>
       </c>
       <c r="C237" s="1" t="inlineStr">
@@ -5920,12 +5915,12 @@
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B238" s="1" t="inlineStr">
         <is>
-          <t>용천제칠격</t>
+          <t>용천제오격</t>
         </is>
       </c>
       <c r="C238" s="1" t="inlineStr">
@@ -5947,12 +5942,12 @@
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>용천제팔격</t>
+          <t>용천제육격</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -5974,12 +5969,12 @@
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B240" s="1" t="inlineStr">
         <is>
-          <t>용천제구격</t>
+          <t>용천제칠격</t>
         </is>
       </c>
       <c r="C240" s="1" t="inlineStr">
@@ -6001,12 +5996,12 @@
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B241" s="1" t="inlineStr">
         <is>
-          <t>용의제일주</t>
+          <t>용천제팔격</t>
         </is>
       </c>
       <c r="C241" s="1" t="inlineStr">
@@ -6028,12 +6023,12 @@
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B242" s="1" t="inlineStr">
         <is>
-          <t>용의제이주</t>
+          <t>용천제구격</t>
         </is>
       </c>
       <c r="C242" s="1" t="inlineStr">
@@ -6055,12 +6050,12 @@
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>용의제삼주</t>
+          <t>용의제일주</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -6082,12 +6077,12 @@
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B244" s="1" t="inlineStr">
         <is>
-          <t>용의제사주</t>
+          <t>용의제이주</t>
         </is>
       </c>
       <c r="C244" s="1" t="inlineStr">
@@ -6109,12 +6104,12 @@
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B245" s="1" t="inlineStr">
         <is>
-          <t>용의제오주</t>
+          <t>용의제삼주</t>
         </is>
       </c>
       <c r="C245" s="1" t="inlineStr">
@@ -6136,12 +6131,12 @@
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B246" s="1" t="inlineStr">
         <is>
-          <t>용의제육주</t>
+          <t>용의제사주</t>
         </is>
       </c>
       <c r="C246" s="1" t="inlineStr">
@@ -6163,12 +6158,12 @@
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B247" s="1" t="inlineStr">
         <is>
-          <t>용의제칠주</t>
+          <t>용의제오주</t>
         </is>
       </c>
       <c r="C247" s="1" t="inlineStr">
@@ -6190,12 +6185,12 @@
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B248" s="1" t="inlineStr">
         <is>
-          <t>용의제팔주</t>
+          <t>용의제육주</t>
         </is>
       </c>
       <c r="C248" s="1" t="inlineStr">
@@ -6217,12 +6212,12 @@
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B249" s="1" t="inlineStr">
         <is>
-          <t>용의제구주</t>
+          <t>용의제칠주</t>
         </is>
       </c>
       <c r="C249" s="1" t="inlineStr">
@@ -6244,12 +6239,12 @@
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>용의제일노</t>
+          <t>용의제팔주</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -6271,12 +6266,12 @@
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B251" s="1" t="inlineStr">
         <is>
-          <t>용의제이노</t>
+          <t>용의제구주</t>
         </is>
       </c>
       <c r="C251" s="1" t="inlineStr">
@@ -6298,12 +6293,12 @@
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B252" s="1" t="inlineStr">
         <is>
-          <t>용의제삼노</t>
+          <t>용의제일노</t>
         </is>
       </c>
       <c r="C252" s="1" t="inlineStr">
@@ -6325,12 +6320,12 @@
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>용의제사노</t>
+          <t>용의제이노</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
@@ -6352,12 +6347,12 @@
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>용의제오노</t>
+          <t>용의제삼노</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -6379,12 +6374,12 @@
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B255" s="1" t="inlineStr">
         <is>
-          <t>용의제육노</t>
+          <t>용의제사노</t>
         </is>
       </c>
       <c r="C255" s="1" t="inlineStr">
@@ -6406,12 +6401,12 @@
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>52</t>
         </is>
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>용의제칠노</t>
+          <t>용의제오노</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
@@ -6433,12 +6428,12 @@
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>53</t>
         </is>
       </c>
       <c r="B257" s="1" t="inlineStr">
         <is>
-          <t>용의제팔노</t>
+          <t>용의제육노</t>
         </is>
       </c>
       <c r="C257" s="1" t="inlineStr">
@@ -6460,12 +6455,12 @@
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>54</t>
         </is>
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>용의제구노</t>
+          <t>용의제칠노</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
@@ -6487,17 +6482,22 @@
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>55</t>
         </is>
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>영후의저주</t>
+          <t>용의제팔노</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
@@ -6509,12 +6509,12 @@
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>56</t>
         </is>
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>반짝반짝</t>
+          <t>용의제구노</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -6536,12 +6536,12 @@
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>57</t>
         </is>
       </c>
       <c r="B261" s="1" t="inlineStr">
         <is>
-          <t>풍령의분노</t>
+          <t>영후의저주</t>
         </is>
       </c>
       <c r="C261" s="1" t="inlineStr">
@@ -6558,17 +6558,22 @@
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>58</t>
         </is>
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>지령의분노</t>
+          <t>반짝반짝</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -6580,22 +6585,17 @@
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>늪의주박</t>
+          <t>풍령의분노</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D263" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E263" s="1" t="inlineStr">
@@ -6607,12 +6607,12 @@
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="B264" s="1" t="inlineStr">
         <is>
-          <t>늪의주박술</t>
+          <t>지령의분노</t>
         </is>
       </c>
       <c r="C264" s="1" t="inlineStr">
@@ -6629,17 +6629,22 @@
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>61</t>
         </is>
       </c>
       <c r="B265" s="1" t="inlineStr">
         <is>
-          <t>귀문진원</t>
+          <t>늪의주박</t>
         </is>
       </c>
       <c r="C265" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E265" s="1" t="inlineStr">
@@ -6651,12 +6656,12 @@
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="B266" s="1" t="inlineStr">
         <is>
-          <t>빛나는연등</t>
+          <t>늪의주박술</t>
         </is>
       </c>
       <c r="C266" s="1" t="inlineStr">
@@ -6673,17 +6678,17 @@
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>63</t>
         </is>
       </c>
       <c r="B267" s="1" t="inlineStr">
         <is>
-          <t>유저조사</t>
+          <t>귀문진원</t>
         </is>
       </c>
       <c r="C267" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E267" s="1" t="inlineStr">
@@ -6695,22 +6700,17 @@
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>64</t>
         </is>
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>일성백열장</t>
+          <t>빛나는연등</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D268" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E268" s="1" t="inlineStr">
@@ -6722,22 +6722,17 @@
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>90</t>
         </is>
       </c>
       <c r="B269" s="1" t="inlineStr">
         <is>
-          <t>이성백열장</t>
+          <t>유저조사</t>
         </is>
       </c>
       <c r="C269" s="1" t="inlineStr">
         <is>
           <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E269" s="1" t="inlineStr">
@@ -6749,12 +6744,12 @@
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>103</t>
         </is>
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>삼성백열장</t>
+          <t>일성백열장</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
@@ -6776,12 +6771,12 @@
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>104</t>
         </is>
       </c>
       <c r="B271" s="1" t="inlineStr">
         <is>
-          <t>사성백열장</t>
+          <t>이성백열장</t>
         </is>
       </c>
       <c r="C271" s="1" t="inlineStr">
@@ -6803,12 +6798,12 @@
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>105</t>
         </is>
       </c>
       <c r="B272" s="1" t="inlineStr">
         <is>
-          <t>오성백열장</t>
+          <t>삼성백열장</t>
         </is>
       </c>
       <c r="C272" s="1" t="inlineStr">
@@ -6830,17 +6825,22 @@
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
         <is>
-          <t>113</t>
+          <t>106</t>
         </is>
       </c>
       <c r="B273" s="1" t="inlineStr">
         <is>
-          <t>금강퇴</t>
+          <t>사성백열장</t>
         </is>
       </c>
       <c r="C273" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E273" s="1" t="inlineStr">
@@ -6852,17 +6852,22 @@
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>107</t>
         </is>
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>일성금강퇴</t>
+          <t>오성백열장</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>TARGET</t>
+        </is>
+      </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
@@ -6874,12 +6879,12 @@
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>113</t>
         </is>
       </c>
       <c r="B275" s="1" t="inlineStr">
         <is>
-          <t>이성금강퇴</t>
+          <t>금강퇴</t>
         </is>
       </c>
       <c r="C275" s="1" t="inlineStr">
@@ -6896,12 +6901,12 @@
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>114</t>
         </is>
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>삼성금강퇴</t>
+          <t>일성금강퇴</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -6918,12 +6923,12 @@
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>115</t>
         </is>
       </c>
       <c r="B277" s="1" t="inlineStr">
         <is>
-          <t>사성금강퇴</t>
+          <t>이성금강퇴</t>
         </is>
       </c>
       <c r="C277" s="1" t="inlineStr">
@@ -6940,12 +6945,12 @@
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>116</t>
         </is>
       </c>
       <c r="B278" s="1" t="inlineStr">
         <is>
-          <t>오성금강퇴</t>
+          <t>삼성금강퇴</t>
         </is>
       </c>
       <c r="C278" s="1" t="inlineStr">
@@ -6962,22 +6967,17 @@
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>117</t>
         </is>
       </c>
       <c r="B279" s="1" t="inlineStr">
         <is>
-          <t>선풍각</t>
+          <t>사성금강퇴</t>
         </is>
       </c>
       <c r="C279" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D279" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E279" s="1" t="inlineStr">
@@ -6989,22 +6989,17 @@
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>118</t>
         </is>
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>일성선풍각</t>
+          <t>오성금강퇴</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
         <is>
-          <t>TARGET</t>
-        </is>
-      </c>
-      <c r="D280" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">대상은? </t>
+          <t>NORMAL</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
@@ -7016,12 +7011,12 @@
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>119</t>
         </is>
       </c>
       <c r="B281" s="1" t="inlineStr">
         <is>
-          <t>이성선풍각</t>
+          <t>선풍각</t>
         </is>
       </c>
       <c r="C281" s="1" t="inlineStr">
@@ -7043,12 +7038,12 @@
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>120</t>
         </is>
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>삼성선풍각</t>
+          <t>일성선풍각</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -7070,12 +7065,12 @@
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>121</t>
         </is>
       </c>
       <c r="B283" s="1" t="inlineStr">
         <is>
-          <t>사성선풍각</t>
+          <t>이성선풍각</t>
         </is>
       </c>
       <c r="C283" s="1" t="inlineStr">
@@ -7097,12 +7092,12 @@
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>122</t>
         </is>
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>오성선풍각</t>
+          <t>삼성선풍각</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -7124,22 +7119,22 @@
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
         <is>
-          <t>126</t>
+          <t>123</t>
         </is>
       </c>
       <c r="B285" s="1" t="inlineStr">
         <is>
-          <t>소림경수둔갑술</t>
+          <t>사성선풍각</t>
         </is>
       </c>
       <c r="C285" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D285" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">변신할 동물은? </t>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E285" s="1" t="inlineStr">
@@ -7151,22 +7146,22 @@
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>124</t>
         </is>
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>소림천구둔갑술</t>
+          <t>오성선풍각</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
         <is>
-          <t>INPUT</t>
+          <t>TARGET</t>
         </is>
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">변신할 동물은? </t>
+          <t xml:space="preserve">대상은? </t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
@@ -7178,12 +7173,12 @@
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>126</t>
         </is>
       </c>
       <c r="B287" s="1" t="inlineStr">
         <is>
-          <t>소림후둔갑술</t>
+          <t>소림경수둔갑술</t>
         </is>
       </c>
       <c r="C287" s="1" t="inlineStr">
@@ -7205,12 +7200,12 @@
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>127</t>
         </is>
       </c>
       <c r="B288" s="1" t="inlineStr">
         <is>
-          <t>소림강시둔갑술</t>
+          <t>소림천구둔갑술</t>
         </is>
       </c>
       <c r="C288" s="1" t="inlineStr">
@@ -7232,12 +7227,12 @@
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>128</t>
         </is>
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>인어장군둔갑술</t>
+          <t>소림후둔갑술</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -7259,12 +7254,12 @@
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>129</t>
         </is>
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>상어장군둔갑술</t>
+          <t>소림강시둔갑술</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
@@ -7286,12 +7281,12 @@
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>130</t>
         </is>
       </c>
       <c r="B291" s="1" t="inlineStr">
         <is>
-          <t>해파리장군둔갑술</t>
+          <t>인어장군둔갑술</t>
         </is>
       </c>
       <c r="C291" s="1" t="inlineStr">
@@ -7313,12 +7308,12 @@
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
         <is>
-          <t>133</t>
+          <t>131</t>
         </is>
       </c>
       <c r="B292" s="1" t="inlineStr">
         <is>
-          <t>마려둔갑술</t>
+          <t>상어장군둔갑술</t>
         </is>
       </c>
       <c r="C292" s="1" t="inlineStr">
@@ -7340,12 +7335,12 @@
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>132</t>
         </is>
       </c>
       <c r="B293" s="1" t="inlineStr">
         <is>
-          <t>철거인둔갑술</t>
+          <t>해파리장군둔갑술</t>
         </is>
       </c>
       <c r="C293" s="1" t="inlineStr">
@@ -7367,12 +7362,12 @@
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>133</t>
         </is>
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>해골왕둔갑술</t>
+          <t>마려둔갑술</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
@@ -7394,12 +7389,12 @@
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>134</t>
         </is>
       </c>
       <c r="B295" s="1" t="inlineStr">
         <is>
-          <t>운랑둔갑술</t>
+          <t>철거인둔갑술</t>
         </is>
       </c>
       <c r="C295" s="1" t="inlineStr">
@@ -7421,12 +7416,12 @@
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>135</t>
         </is>
       </c>
       <c r="B296" s="1" t="inlineStr">
         <is>
-          <t>풍석둔갑술</t>
+          <t>해골왕둔갑술</t>
         </is>
       </c>
       <c r="C296" s="1" t="inlineStr">
@@ -7448,12 +7443,12 @@
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
         <is>
-          <t>138</t>
+          <t>136</t>
         </is>
       </c>
       <c r="B297" s="1" t="inlineStr">
         <is>
-          <t>마계천신둔갑술</t>
+          <t>운랑둔갑술</t>
         </is>
       </c>
       <c r="C297" s="1" t="inlineStr">
@@ -7475,25 +7470,79 @@
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B298" s="1" t="inlineStr">
+        <is>
+          <t>풍석둔갑술</t>
+        </is>
+      </c>
+      <c r="C298" s="1" t="inlineStr">
+        <is>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D298" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변신할 동물은? </t>
+        </is>
+      </c>
+      <c r="E298" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="1" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B299" s="1" t="inlineStr">
+        <is>
+          <t>마계천신둔갑술</t>
+        </is>
+      </c>
+      <c r="C299" s="1" t="inlineStr">
+        <is>
+          <t>INPUT</t>
+        </is>
+      </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">변신할 동물은? </t>
+        </is>
+      </c>
+      <c r="E299" s="1" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="1" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="B298" s="1" t="inlineStr">
+      <c r="B300" s="1" t="inlineStr">
         <is>
           <t>불의천신둔갑술</t>
         </is>
       </c>
-      <c r="C298" s="1" t="inlineStr">
+      <c r="C300" s="1" t="inlineStr">
         <is>
           <t>INPUT</t>
         </is>
       </c>
-      <c r="D298" s="1" t="inlineStr">
+      <c r="D300" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">변신할 동물은? </t>
         </is>
       </c>
-      <c r="E298" s="1" t="inlineStr">
+      <c r="E300" s="1" t="inlineStr">
         <is>
           <t>O</t>
         </is>
